--- a/Catch models/cdat_macarellus_cmsy.xlsx
+++ b/Catch models/cdat_macarellus_cmsy.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="20">
   <si>
     <t>Stock</t>
   </si>
@@ -416,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D433"/>
+  <dimension ref="A1:D593"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1">
@@ -441,7 +441,7 @@
         <v>1989</v>
       </c>
       <c r="C2">
-        <v>1671</v>
+        <v>165.696</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -452,7 +452,7 @@
         <v>1990</v>
       </c>
       <c r="C3">
-        <v>1001</v>
+        <v>207.517</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -463,7 +463,7 @@
         <v>1991</v>
       </c>
       <c r="C4">
-        <v>1263</v>
+        <v>242.225</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -474,7 +474,7 @@
         <v>1992</v>
       </c>
       <c r="C5">
-        <v>2169</v>
+        <v>1116.246</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -485,7 +485,7 @@
         <v>1993</v>
       </c>
       <c r="C6">
-        <v>1427</v>
+        <v>148.56</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -496,7 +496,7 @@
         <v>1994</v>
       </c>
       <c r="C7">
-        <v>1948</v>
+        <v>671.263</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -507,7 +507,7 @@
         <v>1995</v>
       </c>
       <c r="C8">
-        <v>1585</v>
+        <v>868.654</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -518,7 +518,7 @@
         <v>1996</v>
       </c>
       <c r="C9">
-        <v>1751</v>
+        <v>966.037</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -529,7 +529,7 @@
         <v>1997</v>
       </c>
       <c r="C10">
-        <v>2984</v>
+        <v>2194.416</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -540,7 +540,7 @@
         <v>1998</v>
       </c>
       <c r="C11">
-        <v>3015</v>
+        <v>1882.119</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -551,7 +551,7 @@
         <v>1999</v>
       </c>
       <c r="C12">
-        <v>2707</v>
+        <v>1622.012</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -562,7 +562,7 @@
         <v>2000</v>
       </c>
       <c r="C13">
-        <v>1864</v>
+        <v>1075.395</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -573,7 +573,7 @@
         <v>2001</v>
       </c>
       <c r="C14">
-        <v>1379</v>
+        <v>847.7</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -584,7 +584,7 @@
         <v>2002</v>
       </c>
       <c r="C15">
-        <v>2232</v>
+        <v>1751.447</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -595,7 +595,7 @@
         <v>2003</v>
       </c>
       <c r="C16">
-        <v>1830</v>
+        <v>1398.02</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -606,7 +606,7 @@
         <v>2004</v>
       </c>
       <c r="C17">
-        <v>1741</v>
+        <v>1085.991</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -617,7 +617,7 @@
         <v>2005</v>
       </c>
       <c r="C18">
-        <v>2181</v>
+        <v>1460.566</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -628,7 +628,7 @@
         <v>2006</v>
       </c>
       <c r="C19">
-        <v>2627</v>
+        <v>1937.453</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -639,7 +639,7 @@
         <v>2007</v>
       </c>
       <c r="C20">
-        <v>2855</v>
+        <v>2292.716</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -650,7 +650,7 @@
         <v>2008</v>
       </c>
       <c r="C21">
-        <v>2387</v>
+        <v>2033.549</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -661,7 +661,7 @@
         <v>2009</v>
       </c>
       <c r="C22">
-        <v>1771</v>
+        <v>1373.338</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -672,7 +672,7 @@
         <v>2010</v>
       </c>
       <c r="C23">
-        <v>1749</v>
+        <v>1442.3</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -683,7 +683,7 @@
         <v>2011</v>
       </c>
       <c r="C24">
-        <v>2163</v>
+        <v>1911.578</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -694,7 +694,7 @@
         <v>2012</v>
       </c>
       <c r="C25">
-        <v>2643</v>
+        <v>2488.848</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -705,7 +705,7 @@
         <v>2013</v>
       </c>
       <c r="C26">
-        <v>2214</v>
+        <v>2210.106</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -716,7 +716,7 @@
         <v>2014</v>
       </c>
       <c r="C27">
-        <v>151</v>
+        <v>1273.775</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -727,117 +727,117 @@
         <v>2015</v>
       </c>
       <c r="C28">
-        <v>644</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B29">
-        <v>1989</v>
+        <v>2016</v>
       </c>
       <c r="C29">
-        <v>1671</v>
+        <v>186.57</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B30">
-        <v>1990</v>
+        <v>2017</v>
       </c>
       <c r="C30">
-        <v>1001</v>
+        <v>621.994</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B31">
-        <v>1991</v>
+        <v>2018</v>
       </c>
       <c r="C31">
-        <v>1263</v>
+        <v>2216.99</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B32">
-        <v>1992</v>
+        <v>2019</v>
       </c>
       <c r="C32">
-        <v>2169</v>
+        <v>793.841</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B33">
-        <v>1993</v>
+        <v>2020</v>
       </c>
       <c r="C33">
-        <v>1427</v>
+        <v>411.605</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B34">
-        <v>1994</v>
+        <v>2021</v>
       </c>
       <c r="C34">
-        <v>1948</v>
+        <v>155.539</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B35">
-        <v>1995</v>
+        <v>2022</v>
       </c>
       <c r="C35">
-        <v>1585</v>
+        <v>151.855</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B36">
-        <v>1996</v>
+        <v>2023</v>
       </c>
       <c r="C36">
-        <v>1751</v>
+        <v>214.405</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B37">
-        <v>1997</v>
+        <v>2024</v>
       </c>
       <c r="C37">
-        <v>2984</v>
+        <v>286.399</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B38">
-        <v>1998</v>
+        <v>2025</v>
       </c>
       <c r="C38">
-        <v>3015</v>
+        <v>61.892</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -845,10 +845,10 @@
         <v>5</v>
       </c>
       <c r="B39">
-        <v>1999</v>
+        <v>1989</v>
       </c>
       <c r="C39">
-        <v>2707</v>
+        <v>165.696</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -856,10 +856,10 @@
         <v>5</v>
       </c>
       <c r="B40">
-        <v>2000</v>
+        <v>1990</v>
       </c>
       <c r="C40">
-        <v>1864</v>
+        <v>207.517</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -867,10 +867,10 @@
         <v>5</v>
       </c>
       <c r="B41">
-        <v>2001</v>
+        <v>1991</v>
       </c>
       <c r="C41">
-        <v>1379</v>
+        <v>242.225</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -878,10 +878,10 @@
         <v>5</v>
       </c>
       <c r="B42">
-        <v>2002</v>
+        <v>1992</v>
       </c>
       <c r="C42">
-        <v>2232</v>
+        <v>1116.246</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -889,10 +889,10 @@
         <v>5</v>
       </c>
       <c r="B43">
-        <v>2003</v>
+        <v>1993</v>
       </c>
       <c r="C43">
-        <v>1830</v>
+        <v>148.56</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -900,10 +900,10 @@
         <v>5</v>
       </c>
       <c r="B44">
-        <v>2004</v>
+        <v>1994</v>
       </c>
       <c r="C44">
-        <v>1741</v>
+        <v>671.263</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -911,10 +911,10 @@
         <v>5</v>
       </c>
       <c r="B45">
-        <v>2005</v>
+        <v>1995</v>
       </c>
       <c r="C45">
-        <v>2181</v>
+        <v>868.654</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -922,10 +922,10 @@
         <v>5</v>
       </c>
       <c r="B46">
-        <v>2006</v>
+        <v>1996</v>
       </c>
       <c r="C46">
-        <v>2627</v>
+        <v>966.037</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -933,10 +933,10 @@
         <v>5</v>
       </c>
       <c r="B47">
-        <v>2007</v>
+        <v>1997</v>
       </c>
       <c r="C47">
-        <v>2855</v>
+        <v>2194.416</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -944,10 +944,10 @@
         <v>5</v>
       </c>
       <c r="B48">
-        <v>2008</v>
+        <v>1998</v>
       </c>
       <c r="C48">
-        <v>2387</v>
+        <v>1882.119</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -955,10 +955,10 @@
         <v>5</v>
       </c>
       <c r="B49">
-        <v>2009</v>
+        <v>1999</v>
       </c>
       <c r="C49">
-        <v>1771</v>
+        <v>1622.012</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -966,10 +966,10 @@
         <v>5</v>
       </c>
       <c r="B50">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="C50">
-        <v>1749</v>
+        <v>1075.395</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -977,10 +977,10 @@
         <v>5</v>
       </c>
       <c r="B51">
-        <v>2011</v>
+        <v>2001</v>
       </c>
       <c r="C51">
-        <v>2163</v>
+        <v>847.7</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -988,10 +988,10 @@
         <v>5</v>
       </c>
       <c r="B52">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="C52">
-        <v>2643</v>
+        <v>1751.447</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -999,10 +999,10 @@
         <v>5</v>
       </c>
       <c r="B53">
-        <v>2013</v>
+        <v>2003</v>
       </c>
       <c r="C53">
-        <v>2214</v>
+        <v>1398.02</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1010,10 +1010,10 @@
         <v>5</v>
       </c>
       <c r="B54">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="C54">
-        <v>151</v>
+        <v>1085.991</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1021,230 +1021,230 @@
         <v>5</v>
       </c>
       <c r="B55">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="C55">
-        <v>644</v>
+        <v>1460.566</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B56">
-        <v>1989</v>
+        <v>2006</v>
       </c>
       <c r="C56">
-        <v>1671</v>
+        <v>1937.453</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B57">
-        <v>1990</v>
+        <v>2007</v>
       </c>
       <c r="C57">
-        <v>1001</v>
+        <v>2292.716</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B58">
-        <v>1991</v>
+        <v>2008</v>
       </c>
       <c r="C58">
-        <v>1263</v>
+        <v>2033.549</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B59">
-        <v>1992</v>
+        <v>2009</v>
       </c>
       <c r="C59">
-        <v>2169</v>
+        <v>1373.338</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B60">
-        <v>1993</v>
+        <v>2010</v>
       </c>
       <c r="C60">
-        <v>1427</v>
+        <v>1442.3</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B61">
-        <v>1994</v>
+        <v>2011</v>
       </c>
       <c r="C61">
-        <v>1948</v>
+        <v>1911.578</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B62">
-        <v>1995</v>
+        <v>2012</v>
       </c>
       <c r="C62">
-        <v>1585</v>
+        <v>2488.848</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B63">
-        <v>1996</v>
+        <v>2013</v>
       </c>
       <c r="C63">
-        <v>1751</v>
+        <v>2210.106</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B64">
-        <v>1997</v>
+        <v>2014</v>
       </c>
       <c r="C64">
-        <v>2984</v>
+        <v>1273.775</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B65">
-        <v>1998</v>
+        <v>2015</v>
       </c>
       <c r="C65">
-        <v>3015</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B66">
-        <v>1999</v>
+        <v>2016</v>
       </c>
       <c r="C66">
-        <v>2707</v>
+        <v>186.57</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B67">
-        <v>2000</v>
+        <v>2017</v>
       </c>
       <c r="C67">
-        <v>1864</v>
+        <v>621.994</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B68">
-        <v>2001</v>
+        <v>2018</v>
       </c>
       <c r="C68">
-        <v>1379</v>
+        <v>2216.99</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B69">
-        <v>2002</v>
+        <v>2019</v>
       </c>
       <c r="C69">
-        <v>2232</v>
+        <v>793.841</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B70">
-        <v>2003</v>
+        <v>2020</v>
       </c>
       <c r="C70">
-        <v>1830</v>
+        <v>411.605</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B71">
-        <v>2004</v>
+        <v>2021</v>
       </c>
       <c r="C71">
-        <v>1741</v>
+        <v>155.539</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B72">
-        <v>2005</v>
+        <v>2022</v>
       </c>
       <c r="C72">
-        <v>2181</v>
+        <v>151.855</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B73">
-        <v>2006</v>
+        <v>2023</v>
       </c>
       <c r="C73">
-        <v>2627</v>
+        <v>214.405</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B74">
-        <v>2007</v>
+        <v>2024</v>
       </c>
       <c r="C74">
-        <v>2855</v>
+        <v>286.399</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B75">
-        <v>2008</v>
+        <v>2025</v>
       </c>
       <c r="C75">
-        <v>2387</v>
+        <v>61.892</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1252,10 +1252,10 @@
         <v>6</v>
       </c>
       <c r="B76">
-        <v>2009</v>
+        <v>1989</v>
       </c>
       <c r="C76">
-        <v>1771</v>
+        <v>165.696</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1263,10 +1263,10 @@
         <v>6</v>
       </c>
       <c r="B77">
-        <v>2010</v>
+        <v>1990</v>
       </c>
       <c r="C77">
-        <v>1749</v>
+        <v>207.517</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1274,10 +1274,10 @@
         <v>6</v>
       </c>
       <c r="B78">
-        <v>2011</v>
+        <v>1991</v>
       </c>
       <c r="C78">
-        <v>2163</v>
+        <v>242.225</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1285,10 +1285,10 @@
         <v>6</v>
       </c>
       <c r="B79">
-        <v>2012</v>
+        <v>1992</v>
       </c>
       <c r="C79">
-        <v>2643</v>
+        <v>1116.246</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1296,10 +1296,10 @@
         <v>6</v>
       </c>
       <c r="B80">
-        <v>2013</v>
+        <v>1993</v>
       </c>
       <c r="C80">
-        <v>2214</v>
+        <v>148.56</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1307,10 +1307,10 @@
         <v>6</v>
       </c>
       <c r="B81">
-        <v>2014</v>
+        <v>1994</v>
       </c>
       <c r="C81">
-        <v>151</v>
+        <v>671.263</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1318,3871 +1318,5631 @@
         <v>6</v>
       </c>
       <c r="B82">
-        <v>2015</v>
+        <v>1995</v>
       </c>
       <c r="C82">
-        <v>644</v>
+        <v>868.654</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B83">
-        <v>1989</v>
+        <v>1996</v>
       </c>
       <c r="C83">
-        <v>1671</v>
+        <v>966.037</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B84">
-        <v>1990</v>
+        <v>1997</v>
       </c>
       <c r="C84">
-        <v>1001</v>
+        <v>2194.416</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B85">
-        <v>1991</v>
+        <v>1998</v>
       </c>
       <c r="C85">
-        <v>1263</v>
+        <v>1882.119</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B86">
-        <v>1992</v>
+        <v>1999</v>
       </c>
       <c r="C86">
-        <v>2169</v>
+        <v>1622.012</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B87">
-        <v>1993</v>
+        <v>2000</v>
       </c>
       <c r="C87">
-        <v>1427</v>
+        <v>1075.395</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B88">
-        <v>1994</v>
+        <v>2001</v>
       </c>
       <c r="C88">
-        <v>1948</v>
+        <v>847.7</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B89">
-        <v>1995</v>
+        <v>2002</v>
       </c>
       <c r="C89">
-        <v>1585</v>
+        <v>1751.447</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B90">
-        <v>1996</v>
+        <v>2003</v>
       </c>
       <c r="C90">
-        <v>1751</v>
+        <v>1398.02</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B91">
-        <v>1997</v>
+        <v>2004</v>
       </c>
       <c r="C91">
-        <v>2984</v>
+        <v>1085.991</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B92">
-        <v>1998</v>
+        <v>2005</v>
       </c>
       <c r="C92">
-        <v>3015</v>
+        <v>1460.566</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B93">
-        <v>1999</v>
+        <v>2006</v>
       </c>
       <c r="C93">
-        <v>2707</v>
+        <v>1937.453</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B94">
-        <v>2000</v>
+        <v>2007</v>
       </c>
       <c r="C94">
-        <v>1864</v>
+        <v>2292.716</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B95">
-        <v>2001</v>
+        <v>2008</v>
       </c>
       <c r="C95">
-        <v>1379</v>
+        <v>2033.549</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B96">
-        <v>2002</v>
+        <v>2009</v>
       </c>
       <c r="C96">
-        <v>2232</v>
+        <v>1373.338</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B97">
-        <v>2003</v>
+        <v>2010</v>
       </c>
       <c r="C97">
-        <v>1830</v>
+        <v>1442.3</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B98">
-        <v>2004</v>
+        <v>2011</v>
       </c>
       <c r="C98">
-        <v>1741</v>
+        <v>1911.578</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B99">
-        <v>2005</v>
+        <v>2012</v>
       </c>
       <c r="C99">
-        <v>2181</v>
+        <v>2488.848</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B100">
-        <v>2006</v>
+        <v>2013</v>
       </c>
       <c r="C100">
-        <v>2627</v>
+        <v>2210.106</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B101">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="C101">
-        <v>2855</v>
+        <v>1273.775</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B102">
-        <v>2008</v>
+        <v>2015</v>
       </c>
       <c r="C102">
-        <v>2387</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B103">
-        <v>2009</v>
+        <v>2016</v>
       </c>
       <c r="C103">
-        <v>1771</v>
+        <v>186.57</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B104">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="C104">
-        <v>1749</v>
+        <v>621.994</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B105">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="C105">
-        <v>2163</v>
+        <v>2216.99</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B106">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C106">
-        <v>2643</v>
+        <v>793.841</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B107">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C107">
-        <v>2214</v>
+        <v>411.605</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B108">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C108">
-        <v>151</v>
+        <v>155.539</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B109">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C109">
-        <v>644</v>
+        <v>151.855</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B110">
-        <v>1989</v>
+        <v>2023</v>
       </c>
       <c r="C110">
-        <v>1671</v>
+        <v>214.405</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B111">
-        <v>1990</v>
+        <v>2024</v>
       </c>
       <c r="C111">
-        <v>1001</v>
+        <v>286.399</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B112">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="C112">
-        <v>1263</v>
+        <v>61.892</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B113">
-        <v>1992</v>
+        <v>1989</v>
       </c>
       <c r="C113">
-        <v>2169</v>
+        <v>165.696</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B114">
-        <v>1993</v>
+        <v>1990</v>
       </c>
       <c r="C114">
-        <v>1427</v>
+        <v>207.517</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B115">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="C115">
-        <v>1948</v>
+        <v>242.225</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B116">
-        <v>1995</v>
+        <v>1992</v>
       </c>
       <c r="C116">
-        <v>1585</v>
+        <v>1116.246</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B117">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="C117">
-        <v>1751</v>
+        <v>148.56</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B118">
-        <v>1997</v>
+        <v>1994</v>
       </c>
       <c r="C118">
-        <v>2984</v>
+        <v>671.263</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B119">
-        <v>1998</v>
+        <v>1995</v>
       </c>
       <c r="C119">
-        <v>3015</v>
+        <v>868.654</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B120">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="C120">
-        <v>2707</v>
+        <v>966.037</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B121">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="C121">
-        <v>1864</v>
+        <v>2194.416</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B122">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="C122">
-        <v>1379</v>
+        <v>1882.119</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B123">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="C123">
-        <v>2232</v>
+        <v>1622.012</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B124">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="C124">
-        <v>1830</v>
+        <v>1075.395</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B125">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="C125">
-        <v>1741</v>
+        <v>847.7</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B126">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="C126">
-        <v>2181</v>
+        <v>1751.447</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B127">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="C127">
-        <v>2627</v>
+        <v>1398.02</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B128">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="C128">
-        <v>2855</v>
+        <v>1085.991</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B129">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="C129">
-        <v>2387</v>
+        <v>1460.566</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B130">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="C130">
-        <v>1771</v>
+        <v>1937.453</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B131">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="C131">
-        <v>1749</v>
+        <v>2292.716</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B132">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="C132">
-        <v>2163</v>
+        <v>2033.549</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B133">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="C133">
-        <v>2643</v>
+        <v>1373.338</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B134">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C134">
-        <v>2214</v>
+        <v>1442.3</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B135">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C135">
-        <v>151</v>
+        <v>1911.578</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B136">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C136">
-        <v>644</v>
+        <v>2488.848</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B137">
-        <v>1989</v>
+        <v>2013</v>
       </c>
       <c r="C137">
-        <v>1671</v>
+        <v>2210.106</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B138">
-        <v>1990</v>
+        <v>2014</v>
       </c>
       <c r="C138">
-        <v>1001</v>
+        <v>1273.775</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B139">
-        <v>1991</v>
+        <v>2015</v>
       </c>
       <c r="C139">
-        <v>1263</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B140">
-        <v>1992</v>
+        <v>2016</v>
       </c>
       <c r="C140">
-        <v>2169</v>
+        <v>186.57</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B141">
-        <v>1993</v>
+        <v>2017</v>
       </c>
       <c r="C141">
-        <v>1427</v>
+        <v>621.994</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B142">
-        <v>1994</v>
+        <v>2018</v>
       </c>
       <c r="C142">
-        <v>1948</v>
+        <v>2216.99</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B143">
-        <v>1995</v>
+        <v>2019</v>
       </c>
       <c r="C143">
-        <v>1585</v>
+        <v>793.841</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B144">
-        <v>1996</v>
+        <v>2020</v>
       </c>
       <c r="C144">
-        <v>1751</v>
+        <v>411.605</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B145">
-        <v>1997</v>
+        <v>2021</v>
       </c>
       <c r="C145">
-        <v>2984</v>
+        <v>155.539</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B146">
-        <v>1998</v>
+        <v>2022</v>
       </c>
       <c r="C146">
-        <v>3015</v>
+        <v>151.855</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B147">
-        <v>1999</v>
+        <v>2023</v>
       </c>
       <c r="C147">
-        <v>2707</v>
+        <v>214.405</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B148">
-        <v>2000</v>
+        <v>2024</v>
       </c>
       <c r="C148">
-        <v>1864</v>
+        <v>286.399</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B149">
-        <v>2001</v>
+        <v>2025</v>
       </c>
       <c r="C149">
-        <v>1379</v>
+        <v>61.892</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B150">
-        <v>2002</v>
+        <v>1989</v>
       </c>
       <c r="C150">
-        <v>2232</v>
+        <v>165.696</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B151">
-        <v>2003</v>
+        <v>1990</v>
       </c>
       <c r="C151">
-        <v>1830</v>
+        <v>207.517</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B152">
-        <v>2004</v>
+        <v>1991</v>
       </c>
       <c r="C152">
-        <v>1741</v>
+        <v>242.225</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B153">
-        <v>2005</v>
+        <v>1992</v>
       </c>
       <c r="C153">
-        <v>2181</v>
+        <v>1116.246</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B154">
-        <v>2006</v>
+        <v>1993</v>
       </c>
       <c r="C154">
-        <v>2627</v>
+        <v>148.56</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B155">
-        <v>2007</v>
+        <v>1994</v>
       </c>
       <c r="C155">
-        <v>2855</v>
+        <v>671.263</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B156">
-        <v>2008</v>
+        <v>1995</v>
       </c>
       <c r="C156">
-        <v>2387</v>
+        <v>868.654</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B157">
-        <v>2009</v>
+        <v>1996</v>
       </c>
       <c r="C157">
-        <v>1771</v>
+        <v>966.037</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B158">
-        <v>2010</v>
+        <v>1997</v>
       </c>
       <c r="C158">
-        <v>1749</v>
+        <v>2194.416</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B159">
-        <v>2011</v>
+        <v>1998</v>
       </c>
       <c r="C159">
-        <v>2163</v>
+        <v>1882.119</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B160">
-        <v>2012</v>
+        <v>1999</v>
       </c>
       <c r="C160">
-        <v>2643</v>
+        <v>1622.012</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B161">
-        <v>2013</v>
+        <v>2000</v>
       </c>
       <c r="C161">
-        <v>2214</v>
+        <v>1075.395</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B162">
-        <v>2014</v>
+        <v>2001</v>
       </c>
       <c r="C162">
-        <v>151</v>
+        <v>847.7</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B163">
-        <v>2015</v>
+        <v>2002</v>
       </c>
       <c r="C163">
-        <v>644</v>
+        <v>1751.447</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B164">
-        <v>1989</v>
+        <v>2003</v>
       </c>
       <c r="C164">
-        <v>1671</v>
+        <v>1398.02</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B165">
-        <v>1990</v>
+        <v>2004</v>
       </c>
       <c r="C165">
-        <v>1001</v>
+        <v>1085.991</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B166">
-        <v>1991</v>
+        <v>2005</v>
       </c>
       <c r="C166">
-        <v>1263</v>
+        <v>1460.566</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B167">
-        <v>1992</v>
+        <v>2006</v>
       </c>
       <c r="C167">
-        <v>2169</v>
+        <v>1937.453</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B168">
-        <v>1993</v>
+        <v>2007</v>
       </c>
       <c r="C168">
-        <v>1427</v>
+        <v>2292.716</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B169">
-        <v>1994</v>
+        <v>2008</v>
       </c>
       <c r="C169">
-        <v>1948</v>
+        <v>2033.549</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B170">
-        <v>1995</v>
+        <v>2009</v>
       </c>
       <c r="C170">
-        <v>1585</v>
+        <v>1373.338</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B171">
-        <v>1996</v>
+        <v>2010</v>
       </c>
       <c r="C171">
-        <v>1751</v>
+        <v>1442.3</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B172">
-        <v>1997</v>
+        <v>2011</v>
       </c>
       <c r="C172">
-        <v>2984</v>
+        <v>1911.578</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B173">
-        <v>1998</v>
+        <v>2012</v>
       </c>
       <c r="C173">
-        <v>3015</v>
+        <v>2488.848</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B174">
-        <v>1999</v>
+        <v>2013</v>
       </c>
       <c r="C174">
-        <v>2707</v>
+        <v>2210.106</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B175">
-        <v>2000</v>
+        <v>2014</v>
       </c>
       <c r="C175">
-        <v>1864</v>
+        <v>1273.775</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B176">
-        <v>2001</v>
+        <v>2015</v>
       </c>
       <c r="C176">
-        <v>1379</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B177">
-        <v>2002</v>
+        <v>2016</v>
       </c>
       <c r="C177">
-        <v>2232</v>
+        <v>186.57</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B178">
-        <v>2003</v>
+        <v>2017</v>
       </c>
       <c r="C178">
-        <v>1830</v>
+        <v>621.994</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B179">
-        <v>2004</v>
+        <v>2018</v>
       </c>
       <c r="C179">
-        <v>1741</v>
+        <v>2216.99</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B180">
-        <v>2005</v>
+        <v>2019</v>
       </c>
       <c r="C180">
-        <v>2181</v>
+        <v>793.841</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B181">
-        <v>2006</v>
+        <v>2020</v>
       </c>
       <c r="C181">
-        <v>2627</v>
+        <v>411.605</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B182">
-        <v>2007</v>
+        <v>2021</v>
       </c>
       <c r="C182">
-        <v>2855</v>
+        <v>155.539</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B183">
-        <v>2008</v>
+        <v>2022</v>
       </c>
       <c r="C183">
-        <v>2387</v>
+        <v>151.855</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B184">
-        <v>2009</v>
+        <v>2023</v>
       </c>
       <c r="C184">
-        <v>1771</v>
+        <v>214.405</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B185">
-        <v>2010</v>
+        <v>2024</v>
       </c>
       <c r="C185">
-        <v>1749</v>
+        <v>286.399</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B186">
-        <v>2011</v>
+        <v>2025</v>
       </c>
       <c r="C186">
-        <v>2163</v>
+        <v>61.892</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B187">
-        <v>2012</v>
+        <v>1989</v>
       </c>
       <c r="C187">
-        <v>2643</v>
+        <v>165.696</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B188">
-        <v>2013</v>
+        <v>1990</v>
       </c>
       <c r="C188">
-        <v>2214</v>
+        <v>207.517</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B189">
-        <v>2014</v>
+        <v>1991</v>
       </c>
       <c r="C189">
-        <v>151</v>
+        <v>242.225</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B190">
-        <v>2015</v>
+        <v>1992</v>
       </c>
       <c r="C190">
-        <v>644</v>
+        <v>1116.246</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B191">
-        <v>1989</v>
+        <v>1993</v>
       </c>
       <c r="C191">
-        <v>1671</v>
+        <v>148.56</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B192">
-        <v>1990</v>
+        <v>1994</v>
       </c>
       <c r="C192">
-        <v>1001</v>
+        <v>671.263</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B193">
-        <v>1991</v>
+        <v>1995</v>
       </c>
       <c r="C193">
-        <v>1263</v>
+        <v>868.654</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B194">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="C194">
-        <v>2169</v>
+        <v>966.037</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B195">
-        <v>1993</v>
+        <v>1997</v>
       </c>
       <c r="C195">
-        <v>1427</v>
+        <v>2194.416</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B196">
-        <v>1994</v>
+        <v>1998</v>
       </c>
       <c r="C196">
-        <v>1948</v>
+        <v>1882.119</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B197">
-        <v>1995</v>
+        <v>1999</v>
       </c>
       <c r="C197">
-        <v>1585</v>
+        <v>1622.012</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B198">
-        <v>1996</v>
+        <v>2000</v>
       </c>
       <c r="C198">
-        <v>1751</v>
+        <v>1075.395</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B199">
-        <v>1997</v>
+        <v>2001</v>
       </c>
       <c r="C199">
-        <v>2984</v>
+        <v>847.7</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B200">
-        <v>1998</v>
+        <v>2002</v>
       </c>
       <c r="C200">
-        <v>3015</v>
+        <v>1751.447</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B201">
-        <v>1999</v>
+        <v>2003</v>
       </c>
       <c r="C201">
-        <v>2707</v>
+        <v>1398.02</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B202">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="C202">
-        <v>1864</v>
+        <v>1085.991</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B203">
-        <v>2001</v>
+        <v>2005</v>
       </c>
       <c r="C203">
-        <v>1379</v>
+        <v>1460.566</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B204">
-        <v>2002</v>
+        <v>2006</v>
       </c>
       <c r="C204">
-        <v>2232</v>
+        <v>1937.453</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B205">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="C205">
-        <v>1830</v>
+        <v>2292.716</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B206">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="C206">
-        <v>1741</v>
+        <v>2033.549</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B207">
-        <v>2005</v>
+        <v>2009</v>
       </c>
       <c r="C207">
-        <v>2181</v>
+        <v>1373.338</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B208">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="C208">
-        <v>2627</v>
+        <v>1442.3</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B209">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="C209">
-        <v>2855</v>
+        <v>1911.578</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B210">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="C210">
-        <v>2387</v>
+        <v>2488.848</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B211">
-        <v>2009</v>
+        <v>2013</v>
       </c>
       <c r="C211">
-        <v>1771</v>
+        <v>2210.106</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B212">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C212">
-        <v>1749</v>
+        <v>1273.775</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B213">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="C213">
-        <v>2163</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B214">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C214">
-        <v>2643</v>
+        <v>186.57</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B215">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="C215">
-        <v>2214</v>
+        <v>621.994</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B216">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="C216">
-        <v>151</v>
+        <v>2216.99</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B217">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="C217">
-        <v>644</v>
+        <v>793.841</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B218">
-        <v>1989</v>
+        <v>2020</v>
       </c>
       <c r="C218">
-        <v>1671</v>
+        <v>411.605</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B219">
-        <v>1990</v>
+        <v>2021</v>
       </c>
       <c r="C219">
-        <v>1001</v>
+        <v>155.539</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B220">
-        <v>1991</v>
+        <v>2022</v>
       </c>
       <c r="C220">
-        <v>1263</v>
+        <v>151.855</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B221">
-        <v>1992</v>
+        <v>2023</v>
       </c>
       <c r="C221">
-        <v>2169</v>
+        <v>214.405</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B222">
-        <v>1993</v>
+        <v>2024</v>
       </c>
       <c r="C222">
-        <v>1427</v>
+        <v>286.399</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B223">
-        <v>1994</v>
+        <v>2025</v>
       </c>
       <c r="C223">
-        <v>1948</v>
+        <v>61.892</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B224">
-        <v>1995</v>
+        <v>1989</v>
       </c>
       <c r="C224">
-        <v>1585</v>
+        <v>165.696</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B225">
-        <v>1996</v>
+        <v>1990</v>
       </c>
       <c r="C225">
-        <v>1751</v>
+        <v>207.517</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B226">
-        <v>1997</v>
+        <v>1991</v>
       </c>
       <c r="C226">
-        <v>2984</v>
+        <v>242.225</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B227">
-        <v>1998</v>
+        <v>1992</v>
       </c>
       <c r="C227">
-        <v>3015</v>
+        <v>1116.246</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B228">
-        <v>1999</v>
+        <v>1993</v>
       </c>
       <c r="C228">
-        <v>2707</v>
+        <v>148.56</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B229">
-        <v>2000</v>
+        <v>1994</v>
       </c>
       <c r="C229">
-        <v>1864</v>
+        <v>671.263</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B230">
-        <v>2001</v>
+        <v>1995</v>
       </c>
       <c r="C230">
-        <v>1379</v>
+        <v>868.654</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B231">
-        <v>2002</v>
+        <v>1996</v>
       </c>
       <c r="C231">
-        <v>2232</v>
+        <v>966.037</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B232">
-        <v>2003</v>
+        <v>1997</v>
       </c>
       <c r="C232">
-        <v>1830</v>
+        <v>2194.416</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B233">
-        <v>2004</v>
+        <v>1998</v>
       </c>
       <c r="C233">
-        <v>1741</v>
+        <v>1882.119</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B234">
-        <v>2005</v>
+        <v>1999</v>
       </c>
       <c r="C234">
-        <v>2181</v>
+        <v>1622.012</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B235">
-        <v>2006</v>
+        <v>2000</v>
       </c>
       <c r="C235">
-        <v>2627</v>
+        <v>1075.395</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B236">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="C236">
-        <v>2855</v>
+        <v>847.7</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B237">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="C237">
-        <v>2387</v>
+        <v>1751.447</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B238">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="C238">
-        <v>1771</v>
+        <v>1398.02</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B239">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="C239">
-        <v>1749</v>
+        <v>1085.991</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B240">
-        <v>2011</v>
+        <v>2005</v>
       </c>
       <c r="C240">
-        <v>2163</v>
+        <v>1460.566</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B241">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C241">
-        <v>2643</v>
+        <v>1937.453</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B242">
-        <v>2013</v>
+        <v>2007</v>
       </c>
       <c r="C242">
-        <v>2214</v>
+        <v>2292.716</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B243">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="C243">
-        <v>151</v>
+        <v>2033.549</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B244">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="C244">
-        <v>644</v>
+        <v>1373.338</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B245">
-        <v>1989</v>
+        <v>2010</v>
       </c>
       <c r="C245">
-        <v>1671</v>
+        <v>1442.3</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B246">
-        <v>1990</v>
+        <v>2011</v>
       </c>
       <c r="C246">
-        <v>1001</v>
+        <v>1911.578</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B247">
-        <v>1991</v>
+        <v>2012</v>
       </c>
       <c r="C247">
-        <v>1263</v>
+        <v>2488.848</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B248">
-        <v>1992</v>
+        <v>2013</v>
       </c>
       <c r="C248">
-        <v>2169</v>
+        <v>2210.106</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B249">
-        <v>1993</v>
+        <v>2014</v>
       </c>
       <c r="C249">
-        <v>1427</v>
+        <v>1273.775</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B250">
-        <v>1994</v>
+        <v>2015</v>
       </c>
       <c r="C250">
-        <v>1948</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B251">
-        <v>1995</v>
+        <v>2016</v>
       </c>
       <c r="C251">
-        <v>1585</v>
+        <v>186.57</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B252">
-        <v>1996</v>
+        <v>2017</v>
       </c>
       <c r="C252">
-        <v>1751</v>
+        <v>621.994</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B253">
-        <v>1997</v>
+        <v>2018</v>
       </c>
       <c r="C253">
-        <v>2984</v>
+        <v>2216.99</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B254">
-        <v>1998</v>
+        <v>2019</v>
       </c>
       <c r="C254">
-        <v>3015</v>
+        <v>793.841</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B255">
-        <v>1999</v>
+        <v>2020</v>
       </c>
       <c r="C255">
-        <v>2707</v>
+        <v>411.605</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B256">
-        <v>2000</v>
+        <v>2021</v>
       </c>
       <c r="C256">
-        <v>1864</v>
+        <v>155.539</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B257">
-        <v>2001</v>
+        <v>2022</v>
       </c>
       <c r="C257">
-        <v>1379</v>
+        <v>151.855</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B258">
-        <v>2002</v>
+        <v>2023</v>
       </c>
       <c r="C258">
-        <v>2232</v>
+        <v>214.405</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B259">
-        <v>2003</v>
+        <v>2024</v>
       </c>
       <c r="C259">
-        <v>1830</v>
+        <v>286.399</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B260">
-        <v>2004</v>
+        <v>2025</v>
       </c>
       <c r="C260">
-        <v>1741</v>
+        <v>61.892</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B261">
-        <v>2005</v>
+        <v>1989</v>
       </c>
       <c r="C261">
-        <v>2181</v>
+        <v>165.696</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B262">
-        <v>2006</v>
+        <v>1990</v>
       </c>
       <c r="C262">
-        <v>2627</v>
+        <v>207.517</v>
       </c>
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B263">
-        <v>2007</v>
+        <v>1991</v>
       </c>
       <c r="C263">
-        <v>2855</v>
+        <v>242.225</v>
       </c>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B264">
-        <v>2008</v>
+        <v>1992</v>
       </c>
       <c r="C264">
-        <v>2387</v>
+        <v>1116.246</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B265">
-        <v>2009</v>
+        <v>1993</v>
       </c>
       <c r="C265">
-        <v>1771</v>
+        <v>148.56</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B266">
-        <v>2010</v>
+        <v>1994</v>
       </c>
       <c r="C266">
-        <v>1749</v>
+        <v>671.263</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B267">
-        <v>2011</v>
+        <v>1995</v>
       </c>
       <c r="C267">
-        <v>2163</v>
+        <v>868.654</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B268">
-        <v>2012</v>
+        <v>1996</v>
       </c>
       <c r="C268">
-        <v>2643</v>
+        <v>966.037</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B269">
-        <v>2013</v>
+        <v>1997</v>
       </c>
       <c r="C269">
-        <v>2214</v>
+        <v>2194.416</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B270">
-        <v>2014</v>
+        <v>1998</v>
       </c>
       <c r="C270">
-        <v>151</v>
+        <v>1882.119</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B271">
-        <v>2015</v>
+        <v>1999</v>
       </c>
       <c r="C271">
-        <v>644</v>
+        <v>1622.012</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B272">
-        <v>1989</v>
+        <v>2000</v>
       </c>
       <c r="C272">
-        <v>1671</v>
+        <v>1075.395</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B273">
-        <v>1990</v>
+        <v>2001</v>
       </c>
       <c r="C273">
-        <v>1001</v>
+        <v>847.7</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B274">
-        <v>1991</v>
+        <v>2002</v>
       </c>
       <c r="C274">
-        <v>1263</v>
+        <v>1751.447</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B275">
-        <v>1992</v>
+        <v>2003</v>
       </c>
       <c r="C275">
-        <v>2169</v>
+        <v>1398.02</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B276">
-        <v>1993</v>
+        <v>2004</v>
       </c>
       <c r="C276">
-        <v>1427</v>
+        <v>1085.991</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B277">
-        <v>1994</v>
+        <v>2005</v>
       </c>
       <c r="C277">
-        <v>1948</v>
+        <v>1460.566</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B278">
-        <v>1995</v>
+        <v>2006</v>
       </c>
       <c r="C278">
-        <v>1585</v>
+        <v>1937.453</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B279">
-        <v>1996</v>
+        <v>2007</v>
       </c>
       <c r="C279">
-        <v>1751</v>
+        <v>2292.716</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B280">
-        <v>1997</v>
+        <v>2008</v>
       </c>
       <c r="C280">
-        <v>2984</v>
+        <v>2033.549</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B281">
-        <v>1998</v>
+        <v>2009</v>
       </c>
       <c r="C281">
-        <v>3015</v>
+        <v>1373.338</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B282">
-        <v>1999</v>
+        <v>2010</v>
       </c>
       <c r="C282">
-        <v>2707</v>
+        <v>1442.3</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B283">
-        <v>2000</v>
+        <v>2011</v>
       </c>
       <c r="C283">
-        <v>1864</v>
+        <v>1911.578</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B284">
-        <v>2001</v>
+        <v>2012</v>
       </c>
       <c r="C284">
-        <v>1379</v>
+        <v>2488.848</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B285">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="C285">
-        <v>2232</v>
+        <v>2210.106</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B286">
-        <v>2003</v>
+        <v>2014</v>
       </c>
       <c r="C286">
-        <v>1830</v>
+        <v>1273.775</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B287">
-        <v>2004</v>
+        <v>2015</v>
       </c>
       <c r="C287">
-        <v>1741</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B288">
-        <v>2005</v>
+        <v>2016</v>
       </c>
       <c r="C288">
-        <v>2181</v>
+        <v>186.57</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B289">
-        <v>2006</v>
+        <v>2017</v>
       </c>
       <c r="C289">
-        <v>2627</v>
+        <v>621.994</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B290">
-        <v>2007</v>
+        <v>2018</v>
       </c>
       <c r="C290">
-        <v>2855</v>
+        <v>2216.99</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B291">
-        <v>2008</v>
+        <v>2019</v>
       </c>
       <c r="C291">
-        <v>2387</v>
+        <v>793.841</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B292">
-        <v>2009</v>
+        <v>2020</v>
       </c>
       <c r="C292">
-        <v>1771</v>
+        <v>411.605</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B293">
-        <v>2010</v>
+        <v>2021</v>
       </c>
       <c r="C293">
-        <v>1749</v>
+        <v>155.539</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B294">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="C294">
-        <v>2163</v>
+        <v>151.855</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B295">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="C295">
-        <v>2643</v>
+        <v>214.405</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B296">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="C296">
-        <v>2214</v>
+        <v>286.399</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B297">
-        <v>2014</v>
+        <v>2025</v>
       </c>
       <c r="C297">
-        <v>151</v>
+        <v>61.892</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B298">
-        <v>2015</v>
+        <v>1989</v>
       </c>
       <c r="C298">
-        <v>644</v>
+        <v>165.696</v>
       </c>
     </row>
     <row r="299" spans="1:3">
       <c r="A299" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B299">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="C299">
-        <v>1671</v>
+        <v>207.517</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B300">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="C300">
-        <v>1001</v>
+        <v>242.225</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B301">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="C301">
-        <v>1263</v>
+        <v>1116.246</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B302">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="C302">
-        <v>2169</v>
+        <v>148.56</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B303">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="C303">
-        <v>1427</v>
+        <v>671.263</v>
       </c>
     </row>
     <row r="304" spans="1:3">
       <c r="A304" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B304">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="C304">
-        <v>1948</v>
+        <v>868.654</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B305">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="C305">
-        <v>1585</v>
+        <v>966.037</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B306">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="C306">
-        <v>1751</v>
+        <v>2194.416</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B307">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C307">
-        <v>2984</v>
+        <v>1882.119</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B308">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="C308">
-        <v>3015</v>
+        <v>1622.012</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B309">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="C309">
-        <v>2707</v>
+        <v>1075.395</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B310">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="C310">
-        <v>1864</v>
+        <v>847.7</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B311">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C311">
-        <v>1379</v>
+        <v>1751.447</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B312">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="C312">
-        <v>2232</v>
+        <v>1398.02</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B313">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C313">
-        <v>1830</v>
+        <v>1085.991</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B314">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="C314">
-        <v>1741</v>
+        <v>1460.566</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B315">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="C315">
-        <v>2181</v>
+        <v>1937.453</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B316">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="C316">
-        <v>2627</v>
+        <v>2292.716</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B317">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="C317">
-        <v>2855</v>
+        <v>2033.549</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B318">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="C318">
-        <v>2387</v>
+        <v>1373.338</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B319">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="C319">
-        <v>1771</v>
+        <v>1442.3</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B320">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="C320">
-        <v>1749</v>
+        <v>1911.578</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B321">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C321">
-        <v>2163</v>
+        <v>2488.848</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B322">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C322">
-        <v>2643</v>
+        <v>2210.106</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B323">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C323">
-        <v>2214</v>
+        <v>1273.775</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B324">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="C324">
-        <v>151</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B325">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C325">
-        <v>644</v>
+        <v>186.57</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B326">
-        <v>1989</v>
+        <v>2017</v>
       </c>
       <c r="C326">
-        <v>1671</v>
+        <v>621.994</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B327">
-        <v>1990</v>
+        <v>2018</v>
       </c>
       <c r="C327">
-        <v>1001</v>
+        <v>2216.99</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B328">
-        <v>1991</v>
+        <v>2019</v>
       </c>
       <c r="C328">
-        <v>1263</v>
+        <v>793.841</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B329">
-        <v>1992</v>
+        <v>2020</v>
       </c>
       <c r="C329">
-        <v>2169</v>
+        <v>411.605</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B330">
-        <v>1993</v>
+        <v>2021</v>
       </c>
       <c r="C330">
-        <v>1427</v>
+        <v>155.539</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B331">
-        <v>1994</v>
+        <v>2022</v>
       </c>
       <c r="C331">
-        <v>1948</v>
+        <v>151.855</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B332">
-        <v>1995</v>
+        <v>2023</v>
       </c>
       <c r="C332">
-        <v>1585</v>
+        <v>214.405</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B333">
-        <v>1996</v>
+        <v>2024</v>
       </c>
       <c r="C333">
-        <v>1751</v>
+        <v>286.399</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B334">
-        <v>1997</v>
+        <v>2025</v>
       </c>
       <c r="C334">
-        <v>2984</v>
+        <v>61.892</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B335">
-        <v>1998</v>
+        <v>1989</v>
       </c>
       <c r="C335">
-        <v>3015</v>
+        <v>165.696</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B336">
-        <v>1999</v>
+        <v>1990</v>
       </c>
       <c r="C336">
-        <v>2707</v>
+        <v>207.517</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B337">
-        <v>2000</v>
+        <v>1991</v>
       </c>
       <c r="C337">
-        <v>1864</v>
+        <v>242.225</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B338">
-        <v>2001</v>
+        <v>1992</v>
       </c>
       <c r="C338">
-        <v>1379</v>
+        <v>1116.246</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B339">
-        <v>2002</v>
+        <v>1993</v>
       </c>
       <c r="C339">
-        <v>2232</v>
+        <v>148.56</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B340">
-        <v>2003</v>
+        <v>1994</v>
       </c>
       <c r="C340">
-        <v>1830</v>
+        <v>671.263</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B341">
-        <v>2004</v>
+        <v>1995</v>
       </c>
       <c r="C341">
-        <v>1741</v>
+        <v>868.654</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B342">
-        <v>2005</v>
+        <v>1996</v>
       </c>
       <c r="C342">
-        <v>2181</v>
+        <v>966.037</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B343">
-        <v>2006</v>
+        <v>1997</v>
       </c>
       <c r="C343">
-        <v>2627</v>
+        <v>2194.416</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B344">
-        <v>2007</v>
+        <v>1998</v>
       </c>
       <c r="C344">
-        <v>2855</v>
+        <v>1882.119</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B345">
-        <v>2008</v>
+        <v>1999</v>
       </c>
       <c r="C345">
-        <v>2387</v>
+        <v>1622.012</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B346">
-        <v>2009</v>
+        <v>2000</v>
       </c>
       <c r="C346">
-        <v>1771</v>
+        <v>1075.395</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B347">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="C347">
-        <v>1749</v>
+        <v>847.7</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B348">
-        <v>2011</v>
+        <v>2002</v>
       </c>
       <c r="C348">
-        <v>2163</v>
+        <v>1751.447</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B349">
-        <v>2012</v>
+        <v>2003</v>
       </c>
       <c r="C349">
-        <v>2643</v>
+        <v>1398.02</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B350">
-        <v>2013</v>
+        <v>2004</v>
       </c>
       <c r="C350">
-        <v>2214</v>
+        <v>1085.991</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B351">
-        <v>2014</v>
+        <v>2005</v>
       </c>
       <c r="C351">
-        <v>151</v>
+        <v>1460.566</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B352">
-        <v>2015</v>
+        <v>2006</v>
       </c>
       <c r="C352">
-        <v>644</v>
+        <v>1937.453</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B353">
-        <v>1989</v>
+        <v>2007</v>
       </c>
       <c r="C353">
-        <v>1671</v>
+        <v>2292.716</v>
       </c>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B354">
-        <v>1990</v>
+        <v>2008</v>
       </c>
       <c r="C354">
-        <v>1001</v>
+        <v>2033.549</v>
       </c>
     </row>
     <row r="355" spans="1:3">
       <c r="A355" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B355">
-        <v>1991</v>
+        <v>2009</v>
       </c>
       <c r="C355">
-        <v>1263</v>
+        <v>1373.338</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B356">
-        <v>1992</v>
+        <v>2010</v>
       </c>
       <c r="C356">
-        <v>2169</v>
+        <v>1442.3</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B357">
-        <v>1993</v>
+        <v>2011</v>
       </c>
       <c r="C357">
-        <v>1427</v>
+        <v>1911.578</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B358">
-        <v>1994</v>
+        <v>2012</v>
       </c>
       <c r="C358">
-        <v>1948</v>
+        <v>2488.848</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B359">
-        <v>1995</v>
+        <v>2013</v>
       </c>
       <c r="C359">
-        <v>1585</v>
+        <v>2210.106</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B360">
-        <v>1996</v>
+        <v>2014</v>
       </c>
       <c r="C360">
-        <v>1751</v>
+        <v>1273.775</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B361">
-        <v>1997</v>
+        <v>2015</v>
       </c>
       <c r="C361">
-        <v>2984</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B362">
-        <v>1998</v>
+        <v>2016</v>
       </c>
       <c r="C362">
-        <v>3015</v>
+        <v>186.57</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B363">
-        <v>1999</v>
+        <v>2017</v>
       </c>
       <c r="C363">
-        <v>2707</v>
+        <v>621.994</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B364">
-        <v>2000</v>
+        <v>2018</v>
       </c>
       <c r="C364">
-        <v>1864</v>
+        <v>2216.99</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B365">
-        <v>2001</v>
+        <v>2019</v>
       </c>
       <c r="C365">
-        <v>1379</v>
+        <v>793.841</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B366">
-        <v>2002</v>
+        <v>2020</v>
       </c>
       <c r="C366">
-        <v>2232</v>
+        <v>411.605</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B367">
-        <v>2003</v>
+        <v>2021</v>
       </c>
       <c r="C367">
-        <v>1830</v>
+        <v>155.539</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B368">
-        <v>2004</v>
+        <v>2022</v>
       </c>
       <c r="C368">
-        <v>1741</v>
+        <v>151.855</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B369">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="C369">
-        <v>2181</v>
+        <v>214.405</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B370">
-        <v>2006</v>
+        <v>2024</v>
       </c>
       <c r="C370">
-        <v>2627</v>
+        <v>286.399</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B371">
-        <v>2007</v>
+        <v>2025</v>
       </c>
       <c r="C371">
-        <v>2855</v>
+        <v>61.892</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B372">
-        <v>2008</v>
+        <v>1989</v>
       </c>
       <c r="C372">
-        <v>2387</v>
+        <v>165.696</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B373">
-        <v>2009</v>
+        <v>1990</v>
       </c>
       <c r="C373">
-        <v>1771</v>
+        <v>207.517</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B374">
-        <v>2010</v>
+        <v>1991</v>
       </c>
       <c r="C374">
-        <v>1749</v>
+        <v>242.225</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B375">
-        <v>2011</v>
+        <v>1992</v>
       </c>
       <c r="C375">
-        <v>2163</v>
+        <v>1116.246</v>
       </c>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B376">
-        <v>2012</v>
+        <v>1993</v>
       </c>
       <c r="C376">
-        <v>2643</v>
+        <v>148.56</v>
       </c>
     </row>
     <row r="377" spans="1:3">
       <c r="A377" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B377">
-        <v>2013</v>
+        <v>1994</v>
       </c>
       <c r="C377">
-        <v>2214</v>
+        <v>671.263</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B378">
-        <v>2014</v>
+        <v>1995</v>
       </c>
       <c r="C378">
-        <v>151</v>
+        <v>868.654</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B379">
-        <v>2015</v>
+        <v>1996</v>
       </c>
       <c r="C379">
-        <v>644</v>
+        <v>966.037</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B380">
-        <v>1989</v>
+        <v>1997</v>
       </c>
       <c r="C380">
-        <v>1671</v>
+        <v>2194.416</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B381">
-        <v>1990</v>
+        <v>1998</v>
       </c>
       <c r="C381">
-        <v>1001</v>
+        <v>1882.119</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B382">
-        <v>1991</v>
+        <v>1999</v>
       </c>
       <c r="C382">
-        <v>1263</v>
+        <v>1622.012</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B383">
-        <v>1992</v>
+        <v>2000</v>
       </c>
       <c r="C383">
-        <v>2169</v>
+        <v>1075.395</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B384">
-        <v>1993</v>
+        <v>2001</v>
       </c>
       <c r="C384">
-        <v>1427</v>
+        <v>847.7</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B385">
-        <v>1994</v>
+        <v>2002</v>
       </c>
       <c r="C385">
-        <v>1948</v>
+        <v>1751.447</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B386">
-        <v>1995</v>
+        <v>2003</v>
       </c>
       <c r="C386">
-        <v>1585</v>
+        <v>1398.02</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B387">
-        <v>1996</v>
+        <v>2004</v>
       </c>
       <c r="C387">
-        <v>1751</v>
+        <v>1085.991</v>
       </c>
     </row>
     <row r="388" spans="1:3">
       <c r="A388" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B388">
-        <v>1997</v>
+        <v>2005</v>
       </c>
       <c r="C388">
-        <v>2984</v>
+        <v>1460.566</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B389">
-        <v>1998</v>
+        <v>2006</v>
       </c>
       <c r="C389">
-        <v>3015</v>
+        <v>1937.453</v>
       </c>
     </row>
     <row r="390" spans="1:3">
       <c r="A390" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B390">
-        <v>1999</v>
+        <v>2007</v>
       </c>
       <c r="C390">
-        <v>2707</v>
+        <v>2292.716</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B391">
-        <v>2000</v>
+        <v>2008</v>
       </c>
       <c r="C391">
-        <v>1864</v>
+        <v>2033.549</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B392">
-        <v>2001</v>
+        <v>2009</v>
       </c>
       <c r="C392">
-        <v>1379</v>
+        <v>1373.338</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B393">
-        <v>2002</v>
+        <v>2010</v>
       </c>
       <c r="C393">
-        <v>2232</v>
+        <v>1442.3</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B394">
-        <v>2003</v>
+        <v>2011</v>
       </c>
       <c r="C394">
-        <v>1830</v>
+        <v>1911.578</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B395">
-        <v>2004</v>
+        <v>2012</v>
       </c>
       <c r="C395">
-        <v>1741</v>
+        <v>2488.848</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B396">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="C396">
-        <v>2181</v>
+        <v>2210.106</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B397">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C397">
-        <v>2627</v>
+        <v>1273.775</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B398">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="C398">
-        <v>2855</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B399">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C399">
-        <v>2387</v>
+        <v>186.57</v>
       </c>
     </row>
     <row r="400" spans="1:3">
       <c r="A400" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B400">
-        <v>2009</v>
+        <v>2017</v>
       </c>
       <c r="C400">
-        <v>1771</v>
+        <v>621.994</v>
       </c>
     </row>
     <row r="401" spans="1:3">
       <c r="A401" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B401">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C401">
-        <v>1749</v>
+        <v>2216.99</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B402">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C402">
-        <v>2163</v>
+        <v>793.841</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B403">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C403">
-        <v>2643</v>
+        <v>411.605</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B404">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="C404">
-        <v>2214</v>
+        <v>155.539</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B405">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C405">
-        <v>151</v>
+        <v>151.855</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B406">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="C406">
-        <v>644</v>
+        <v>214.405</v>
       </c>
     </row>
     <row r="407" spans="1:3">
       <c r="A407" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B407">
-        <v>1989</v>
+        <v>2024</v>
       </c>
       <c r="C407">
-        <v>1671</v>
+        <v>286.399</v>
       </c>
     </row>
     <row r="408" spans="1:3">
       <c r="A408" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B408">
-        <v>1990</v>
+        <v>2025</v>
       </c>
       <c r="C408">
-        <v>1001</v>
+        <v>61.892</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B409">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="C409">
-        <v>1263</v>
+        <v>165.696</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B410">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="C410">
-        <v>2169</v>
+        <v>207.517</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B411">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="C411">
-        <v>1427</v>
+        <v>242.225</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B412">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="C412">
-        <v>1948</v>
+        <v>1116.246</v>
       </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B413">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="C413">
-        <v>1585</v>
+        <v>148.56</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B414">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="C414">
-        <v>1751</v>
+        <v>671.263</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B415">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="C415">
-        <v>2984</v>
+        <v>868.654</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B416">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="C416">
-        <v>3015</v>
+        <v>966.037</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B417">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="C417">
-        <v>2707</v>
+        <v>2194.416</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B418">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="C418">
-        <v>1864</v>
+        <v>1882.119</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B419">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="C419">
-        <v>1379</v>
+        <v>1622.012</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B420">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="C420">
-        <v>2232</v>
+        <v>1075.395</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B421">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C421">
-        <v>1830</v>
+        <v>847.7</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B422">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="C422">
-        <v>1741</v>
+        <v>1751.447</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B423">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="C423">
-        <v>2181</v>
+        <v>1398.02</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B424">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="C424">
-        <v>2627</v>
+        <v>1085.991</v>
       </c>
     </row>
     <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B425">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="C425">
-        <v>2855</v>
+        <v>1460.566</v>
       </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B426">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C426">
-        <v>2387</v>
+        <v>1937.453</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B427">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="C427">
-        <v>1771</v>
+        <v>2292.716</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B428">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C428">
-        <v>1749</v>
+        <v>2033.549</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B429">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="C429">
-        <v>2163</v>
+        <v>1373.338</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B430">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C430">
-        <v>2643</v>
+        <v>1442.3</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B431">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C431">
-        <v>2214</v>
+        <v>1911.578</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B432">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C432">
-        <v>151</v>
+        <v>2488.848</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
+        <v>15</v>
+      </c>
+      <c r="B433">
+        <v>2013</v>
+      </c>
+      <c r="C433">
+        <v>2210.106</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3">
+      <c r="A434" t="s">
+        <v>15</v>
+      </c>
+      <c r="B434">
+        <v>2014</v>
+      </c>
+      <c r="C434">
+        <v>1273.775</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3">
+      <c r="A435" t="s">
+        <v>15</v>
+      </c>
+      <c r="B435">
+        <v>2015</v>
+      </c>
+      <c r="C435">
+        <v>24.05</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3">
+      <c r="A436" t="s">
+        <v>15</v>
+      </c>
+      <c r="B436">
+        <v>2016</v>
+      </c>
+      <c r="C436">
+        <v>186.57</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3">
+      <c r="A437" t="s">
+        <v>15</v>
+      </c>
+      <c r="B437">
+        <v>2017</v>
+      </c>
+      <c r="C437">
+        <v>621.994</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3">
+      <c r="A438" t="s">
+        <v>15</v>
+      </c>
+      <c r="B438">
+        <v>2018</v>
+      </c>
+      <c r="C438">
+        <v>2216.99</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3">
+      <c r="A439" t="s">
+        <v>15</v>
+      </c>
+      <c r="B439">
+        <v>2019</v>
+      </c>
+      <c r="C439">
+        <v>793.841</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3">
+      <c r="A440" t="s">
+        <v>15</v>
+      </c>
+      <c r="B440">
+        <v>2020</v>
+      </c>
+      <c r="C440">
+        <v>411.605</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3">
+      <c r="A441" t="s">
+        <v>15</v>
+      </c>
+      <c r="B441">
+        <v>2021</v>
+      </c>
+      <c r="C441">
+        <v>155.539</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3">
+      <c r="A442" t="s">
+        <v>15</v>
+      </c>
+      <c r="B442">
+        <v>2022</v>
+      </c>
+      <c r="C442">
+        <v>151.855</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3">
+      <c r="A443" t="s">
+        <v>15</v>
+      </c>
+      <c r="B443">
+        <v>2023</v>
+      </c>
+      <c r="C443">
+        <v>214.405</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3">
+      <c r="A444" t="s">
+        <v>15</v>
+      </c>
+      <c r="B444">
+        <v>2024</v>
+      </c>
+      <c r="C444">
+        <v>286.399</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3">
+      <c r="A445" t="s">
+        <v>15</v>
+      </c>
+      <c r="B445">
+        <v>2025</v>
+      </c>
+      <c r="C445">
+        <v>61.892</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3">
+      <c r="A446" t="s">
+        <v>16</v>
+      </c>
+      <c r="B446">
+        <v>1989</v>
+      </c>
+      <c r="C446">
+        <v>165.696</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3">
+      <c r="A447" t="s">
+        <v>16</v>
+      </c>
+      <c r="B447">
+        <v>1990</v>
+      </c>
+      <c r="C447">
+        <v>207.517</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3">
+      <c r="A448" t="s">
+        <v>16</v>
+      </c>
+      <c r="B448">
+        <v>1991</v>
+      </c>
+      <c r="C448">
+        <v>242.225</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3">
+      <c r="A449" t="s">
+        <v>16</v>
+      </c>
+      <c r="B449">
+        <v>1992</v>
+      </c>
+      <c r="C449">
+        <v>1116.246</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3">
+      <c r="A450" t="s">
+        <v>16</v>
+      </c>
+      <c r="B450">
+        <v>1993</v>
+      </c>
+      <c r="C450">
+        <v>148.56</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3">
+      <c r="A451" t="s">
+        <v>16</v>
+      </c>
+      <c r="B451">
+        <v>1994</v>
+      </c>
+      <c r="C451">
+        <v>671.263</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3">
+      <c r="A452" t="s">
+        <v>16</v>
+      </c>
+      <c r="B452">
+        <v>1995</v>
+      </c>
+      <c r="C452">
+        <v>868.654</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3">
+      <c r="A453" t="s">
+        <v>16</v>
+      </c>
+      <c r="B453">
+        <v>1996</v>
+      </c>
+      <c r="C453">
+        <v>966.037</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3">
+      <c r="A454" t="s">
+        <v>16</v>
+      </c>
+      <c r="B454">
+        <v>1997</v>
+      </c>
+      <c r="C454">
+        <v>2194.416</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3">
+      <c r="A455" t="s">
+        <v>16</v>
+      </c>
+      <c r="B455">
+        <v>1998</v>
+      </c>
+      <c r="C455">
+        <v>1882.119</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3">
+      <c r="A456" t="s">
+        <v>16</v>
+      </c>
+      <c r="B456">
+        <v>1999</v>
+      </c>
+      <c r="C456">
+        <v>1622.012</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3">
+      <c r="A457" t="s">
+        <v>16</v>
+      </c>
+      <c r="B457">
+        <v>2000</v>
+      </c>
+      <c r="C457">
+        <v>1075.395</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3">
+      <c r="A458" t="s">
+        <v>16</v>
+      </c>
+      <c r="B458">
+        <v>2001</v>
+      </c>
+      <c r="C458">
+        <v>847.7</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3">
+      <c r="A459" t="s">
+        <v>16</v>
+      </c>
+      <c r="B459">
+        <v>2002</v>
+      </c>
+      <c r="C459">
+        <v>1751.447</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3">
+      <c r="A460" t="s">
+        <v>16</v>
+      </c>
+      <c r="B460">
+        <v>2003</v>
+      </c>
+      <c r="C460">
+        <v>1398.02</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3">
+      <c r="A461" t="s">
+        <v>16</v>
+      </c>
+      <c r="B461">
+        <v>2004</v>
+      </c>
+      <c r="C461">
+        <v>1085.991</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3">
+      <c r="A462" t="s">
+        <v>16</v>
+      </c>
+      <c r="B462">
+        <v>2005</v>
+      </c>
+      <c r="C462">
+        <v>1460.566</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3">
+      <c r="A463" t="s">
+        <v>16</v>
+      </c>
+      <c r="B463">
+        <v>2006</v>
+      </c>
+      <c r="C463">
+        <v>1937.453</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3">
+      <c r="A464" t="s">
+        <v>16</v>
+      </c>
+      <c r="B464">
+        <v>2007</v>
+      </c>
+      <c r="C464">
+        <v>2292.716</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3">
+      <c r="A465" t="s">
+        <v>16</v>
+      </c>
+      <c r="B465">
+        <v>2008</v>
+      </c>
+      <c r="C465">
+        <v>2033.549</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3">
+      <c r="A466" t="s">
+        <v>16</v>
+      </c>
+      <c r="B466">
+        <v>2009</v>
+      </c>
+      <c r="C466">
+        <v>1373.338</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3">
+      <c r="A467" t="s">
+        <v>16</v>
+      </c>
+      <c r="B467">
+        <v>2010</v>
+      </c>
+      <c r="C467">
+        <v>1442.3</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3">
+      <c r="A468" t="s">
+        <v>16</v>
+      </c>
+      <c r="B468">
+        <v>2011</v>
+      </c>
+      <c r="C468">
+        <v>1911.578</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3">
+      <c r="A469" t="s">
+        <v>16</v>
+      </c>
+      <c r="B469">
+        <v>2012</v>
+      </c>
+      <c r="C469">
+        <v>2488.848</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3">
+      <c r="A470" t="s">
+        <v>16</v>
+      </c>
+      <c r="B470">
+        <v>2013</v>
+      </c>
+      <c r="C470">
+        <v>2210.106</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3">
+      <c r="A471" t="s">
+        <v>16</v>
+      </c>
+      <c r="B471">
+        <v>2014</v>
+      </c>
+      <c r="C471">
+        <v>1273.775</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3">
+      <c r="A472" t="s">
+        <v>16</v>
+      </c>
+      <c r="B472">
+        <v>2015</v>
+      </c>
+      <c r="C472">
+        <v>24.05</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3">
+      <c r="A473" t="s">
+        <v>16</v>
+      </c>
+      <c r="B473">
+        <v>2016</v>
+      </c>
+      <c r="C473">
+        <v>186.57</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3">
+      <c r="A474" t="s">
+        <v>16</v>
+      </c>
+      <c r="B474">
+        <v>2017</v>
+      </c>
+      <c r="C474">
+        <v>621.994</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3">
+      <c r="A475" t="s">
+        <v>16</v>
+      </c>
+      <c r="B475">
+        <v>2018</v>
+      </c>
+      <c r="C475">
+        <v>2216.99</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3">
+      <c r="A476" t="s">
+        <v>16</v>
+      </c>
+      <c r="B476">
+        <v>2019</v>
+      </c>
+      <c r="C476">
+        <v>793.841</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3">
+      <c r="A477" t="s">
+        <v>16</v>
+      </c>
+      <c r="B477">
+        <v>2020</v>
+      </c>
+      <c r="C477">
+        <v>411.605</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3">
+      <c r="A478" t="s">
+        <v>16</v>
+      </c>
+      <c r="B478">
+        <v>2021</v>
+      </c>
+      <c r="C478">
+        <v>155.539</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3">
+      <c r="A479" t="s">
+        <v>16</v>
+      </c>
+      <c r="B479">
+        <v>2022</v>
+      </c>
+      <c r="C479">
+        <v>151.855</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3">
+      <c r="A480" t="s">
+        <v>16</v>
+      </c>
+      <c r="B480">
+        <v>2023</v>
+      </c>
+      <c r="C480">
+        <v>214.405</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3">
+      <c r="A481" t="s">
+        <v>16</v>
+      </c>
+      <c r="B481">
+        <v>2024</v>
+      </c>
+      <c r="C481">
+        <v>286.399</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3">
+      <c r="A482" t="s">
+        <v>16</v>
+      </c>
+      <c r="B482">
+        <v>2025</v>
+      </c>
+      <c r="C482">
+        <v>61.892</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3">
+      <c r="A483" t="s">
+        <v>17</v>
+      </c>
+      <c r="B483">
+        <v>1989</v>
+      </c>
+      <c r="C483">
+        <v>165.696</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3">
+      <c r="A484" t="s">
+        <v>17</v>
+      </c>
+      <c r="B484">
+        <v>1990</v>
+      </c>
+      <c r="C484">
+        <v>207.517</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3">
+      <c r="A485" t="s">
+        <v>17</v>
+      </c>
+      <c r="B485">
+        <v>1991</v>
+      </c>
+      <c r="C485">
+        <v>242.225</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3">
+      <c r="A486" t="s">
+        <v>17</v>
+      </c>
+      <c r="B486">
+        <v>1992</v>
+      </c>
+      <c r="C486">
+        <v>1116.246</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3">
+      <c r="A487" t="s">
+        <v>17</v>
+      </c>
+      <c r="B487">
+        <v>1993</v>
+      </c>
+      <c r="C487">
+        <v>148.56</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3">
+      <c r="A488" t="s">
+        <v>17</v>
+      </c>
+      <c r="B488">
+        <v>1994</v>
+      </c>
+      <c r="C488">
+        <v>671.263</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3">
+      <c r="A489" t="s">
+        <v>17</v>
+      </c>
+      <c r="B489">
+        <v>1995</v>
+      </c>
+      <c r="C489">
+        <v>868.654</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3">
+      <c r="A490" t="s">
+        <v>17</v>
+      </c>
+      <c r="B490">
+        <v>1996</v>
+      </c>
+      <c r="C490">
+        <v>966.037</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3">
+      <c r="A491" t="s">
+        <v>17</v>
+      </c>
+      <c r="B491">
+        <v>1997</v>
+      </c>
+      <c r="C491">
+        <v>2194.416</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3">
+      <c r="A492" t="s">
+        <v>17</v>
+      </c>
+      <c r="B492">
+        <v>1998</v>
+      </c>
+      <c r="C492">
+        <v>1882.119</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3">
+      <c r="A493" t="s">
+        <v>17</v>
+      </c>
+      <c r="B493">
+        <v>1999</v>
+      </c>
+      <c r="C493">
+        <v>1622.012</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3">
+      <c r="A494" t="s">
+        <v>17</v>
+      </c>
+      <c r="B494">
+        <v>2000</v>
+      </c>
+      <c r="C494">
+        <v>1075.395</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3">
+      <c r="A495" t="s">
+        <v>17</v>
+      </c>
+      <c r="B495">
+        <v>2001</v>
+      </c>
+      <c r="C495">
+        <v>847.7</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3">
+      <c r="A496" t="s">
+        <v>17</v>
+      </c>
+      <c r="B496">
+        <v>2002</v>
+      </c>
+      <c r="C496">
+        <v>1751.447</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3">
+      <c r="A497" t="s">
+        <v>17</v>
+      </c>
+      <c r="B497">
+        <v>2003</v>
+      </c>
+      <c r="C497">
+        <v>1398.02</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3">
+      <c r="A498" t="s">
+        <v>17</v>
+      </c>
+      <c r="B498">
+        <v>2004</v>
+      </c>
+      <c r="C498">
+        <v>1085.991</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3">
+      <c r="A499" t="s">
+        <v>17</v>
+      </c>
+      <c r="B499">
+        <v>2005</v>
+      </c>
+      <c r="C499">
+        <v>1460.566</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3">
+      <c r="A500" t="s">
+        <v>17</v>
+      </c>
+      <c r="B500">
+        <v>2006</v>
+      </c>
+      <c r="C500">
+        <v>1937.453</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3">
+      <c r="A501" t="s">
+        <v>17</v>
+      </c>
+      <c r="B501">
+        <v>2007</v>
+      </c>
+      <c r="C501">
+        <v>2292.716</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3">
+      <c r="A502" t="s">
+        <v>17</v>
+      </c>
+      <c r="B502">
+        <v>2008</v>
+      </c>
+      <c r="C502">
+        <v>2033.549</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3">
+      <c r="A503" t="s">
+        <v>17</v>
+      </c>
+      <c r="B503">
+        <v>2009</v>
+      </c>
+      <c r="C503">
+        <v>1373.338</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3">
+      <c r="A504" t="s">
+        <v>17</v>
+      </c>
+      <c r="B504">
+        <v>2010</v>
+      </c>
+      <c r="C504">
+        <v>1442.3</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3">
+      <c r="A505" t="s">
+        <v>17</v>
+      </c>
+      <c r="B505">
+        <v>2011</v>
+      </c>
+      <c r="C505">
+        <v>1911.578</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3">
+      <c r="A506" t="s">
+        <v>17</v>
+      </c>
+      <c r="B506">
+        <v>2012</v>
+      </c>
+      <c r="C506">
+        <v>2488.848</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3">
+      <c r="A507" t="s">
+        <v>17</v>
+      </c>
+      <c r="B507">
+        <v>2013</v>
+      </c>
+      <c r="C507">
+        <v>2210.106</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3">
+      <c r="A508" t="s">
+        <v>17</v>
+      </c>
+      <c r="B508">
+        <v>2014</v>
+      </c>
+      <c r="C508">
+        <v>1273.775</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3">
+      <c r="A509" t="s">
+        <v>17</v>
+      </c>
+      <c r="B509">
+        <v>2015</v>
+      </c>
+      <c r="C509">
+        <v>24.05</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3">
+      <c r="A510" t="s">
+        <v>17</v>
+      </c>
+      <c r="B510">
+        <v>2016</v>
+      </c>
+      <c r="C510">
+        <v>186.57</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3">
+      <c r="A511" t="s">
+        <v>17</v>
+      </c>
+      <c r="B511">
+        <v>2017</v>
+      </c>
+      <c r="C511">
+        <v>621.994</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3">
+      <c r="A512" t="s">
+        <v>17</v>
+      </c>
+      <c r="B512">
+        <v>2018</v>
+      </c>
+      <c r="C512">
+        <v>2216.99</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3">
+      <c r="A513" t="s">
+        <v>17</v>
+      </c>
+      <c r="B513">
+        <v>2019</v>
+      </c>
+      <c r="C513">
+        <v>793.841</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3">
+      <c r="A514" t="s">
+        <v>17</v>
+      </c>
+      <c r="B514">
+        <v>2020</v>
+      </c>
+      <c r="C514">
+        <v>411.605</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3">
+      <c r="A515" t="s">
+        <v>17</v>
+      </c>
+      <c r="B515">
+        <v>2021</v>
+      </c>
+      <c r="C515">
+        <v>155.539</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3">
+      <c r="A516" t="s">
+        <v>17</v>
+      </c>
+      <c r="B516">
+        <v>2022</v>
+      </c>
+      <c r="C516">
+        <v>151.855</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3">
+      <c r="A517" t="s">
+        <v>17</v>
+      </c>
+      <c r="B517">
+        <v>2023</v>
+      </c>
+      <c r="C517">
+        <v>214.405</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3">
+      <c r="A518" t="s">
+        <v>17</v>
+      </c>
+      <c r="B518">
+        <v>2024</v>
+      </c>
+      <c r="C518">
+        <v>286.399</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3">
+      <c r="A519" t="s">
+        <v>17</v>
+      </c>
+      <c r="B519">
+        <v>2025</v>
+      </c>
+      <c r="C519">
+        <v>61.892</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3">
+      <c r="A520" t="s">
+        <v>18</v>
+      </c>
+      <c r="B520">
+        <v>1989</v>
+      </c>
+      <c r="C520">
+        <v>165.696</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3">
+      <c r="A521" t="s">
+        <v>18</v>
+      </c>
+      <c r="B521">
+        <v>1990</v>
+      </c>
+      <c r="C521">
+        <v>207.517</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3">
+      <c r="A522" t="s">
+        <v>18</v>
+      </c>
+      <c r="B522">
+        <v>1991</v>
+      </c>
+      <c r="C522">
+        <v>242.225</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3">
+      <c r="A523" t="s">
+        <v>18</v>
+      </c>
+      <c r="B523">
+        <v>1992</v>
+      </c>
+      <c r="C523">
+        <v>1116.246</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3">
+      <c r="A524" t="s">
+        <v>18</v>
+      </c>
+      <c r="B524">
+        <v>1993</v>
+      </c>
+      <c r="C524">
+        <v>148.56</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3">
+      <c r="A525" t="s">
+        <v>18</v>
+      </c>
+      <c r="B525">
+        <v>1994</v>
+      </c>
+      <c r="C525">
+        <v>671.263</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3">
+      <c r="A526" t="s">
+        <v>18</v>
+      </c>
+      <c r="B526">
+        <v>1995</v>
+      </c>
+      <c r="C526">
+        <v>868.654</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3">
+      <c r="A527" t="s">
+        <v>18</v>
+      </c>
+      <c r="B527">
+        <v>1996</v>
+      </c>
+      <c r="C527">
+        <v>966.037</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3">
+      <c r="A528" t="s">
+        <v>18</v>
+      </c>
+      <c r="B528">
+        <v>1997</v>
+      </c>
+      <c r="C528">
+        <v>2194.416</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3">
+      <c r="A529" t="s">
+        <v>18</v>
+      </c>
+      <c r="B529">
+        <v>1998</v>
+      </c>
+      <c r="C529">
+        <v>1882.119</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3">
+      <c r="A530" t="s">
+        <v>18</v>
+      </c>
+      <c r="B530">
+        <v>1999</v>
+      </c>
+      <c r="C530">
+        <v>1622.012</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3">
+      <c r="A531" t="s">
+        <v>18</v>
+      </c>
+      <c r="B531">
+        <v>2000</v>
+      </c>
+      <c r="C531">
+        <v>1075.395</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3">
+      <c r="A532" t="s">
+        <v>18</v>
+      </c>
+      <c r="B532">
+        <v>2001</v>
+      </c>
+      <c r="C532">
+        <v>847.7</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3">
+      <c r="A533" t="s">
+        <v>18</v>
+      </c>
+      <c r="B533">
+        <v>2002</v>
+      </c>
+      <c r="C533">
+        <v>1751.447</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3">
+      <c r="A534" t="s">
+        <v>18</v>
+      </c>
+      <c r="B534">
+        <v>2003</v>
+      </c>
+      <c r="C534">
+        <v>1398.02</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3">
+      <c r="A535" t="s">
+        <v>18</v>
+      </c>
+      <c r="B535">
+        <v>2004</v>
+      </c>
+      <c r="C535">
+        <v>1085.991</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3">
+      <c r="A536" t="s">
+        <v>18</v>
+      </c>
+      <c r="B536">
+        <v>2005</v>
+      </c>
+      <c r="C536">
+        <v>1460.566</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3">
+      <c r="A537" t="s">
+        <v>18</v>
+      </c>
+      <c r="B537">
+        <v>2006</v>
+      </c>
+      <c r="C537">
+        <v>1937.453</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3">
+      <c r="A538" t="s">
+        <v>18</v>
+      </c>
+      <c r="B538">
+        <v>2007</v>
+      </c>
+      <c r="C538">
+        <v>2292.716</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3">
+      <c r="A539" t="s">
+        <v>18</v>
+      </c>
+      <c r="B539">
+        <v>2008</v>
+      </c>
+      <c r="C539">
+        <v>2033.549</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3">
+      <c r="A540" t="s">
+        <v>18</v>
+      </c>
+      <c r="B540">
+        <v>2009</v>
+      </c>
+      <c r="C540">
+        <v>1373.338</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3">
+      <c r="A541" t="s">
+        <v>18</v>
+      </c>
+      <c r="B541">
+        <v>2010</v>
+      </c>
+      <c r="C541">
+        <v>1442.3</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3">
+      <c r="A542" t="s">
+        <v>18</v>
+      </c>
+      <c r="B542">
+        <v>2011</v>
+      </c>
+      <c r="C542">
+        <v>1911.578</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3">
+      <c r="A543" t="s">
+        <v>18</v>
+      </c>
+      <c r="B543">
+        <v>2012</v>
+      </c>
+      <c r="C543">
+        <v>2488.848</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3">
+      <c r="A544" t="s">
+        <v>18</v>
+      </c>
+      <c r="B544">
+        <v>2013</v>
+      </c>
+      <c r="C544">
+        <v>2210.106</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3">
+      <c r="A545" t="s">
+        <v>18</v>
+      </c>
+      <c r="B545">
+        <v>2014</v>
+      </c>
+      <c r="C545">
+        <v>1273.775</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3">
+      <c r="A546" t="s">
+        <v>18</v>
+      </c>
+      <c r="B546">
+        <v>2015</v>
+      </c>
+      <c r="C546">
+        <v>24.05</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3">
+      <c r="A547" t="s">
+        <v>18</v>
+      </c>
+      <c r="B547">
+        <v>2016</v>
+      </c>
+      <c r="C547">
+        <v>186.57</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3">
+      <c r="A548" t="s">
+        <v>18</v>
+      </c>
+      <c r="B548">
+        <v>2017</v>
+      </c>
+      <c r="C548">
+        <v>621.994</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3">
+      <c r="A549" t="s">
+        <v>18</v>
+      </c>
+      <c r="B549">
+        <v>2018</v>
+      </c>
+      <c r="C549">
+        <v>2216.99</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3">
+      <c r="A550" t="s">
+        <v>18</v>
+      </c>
+      <c r="B550">
+        <v>2019</v>
+      </c>
+      <c r="C550">
+        <v>793.841</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3">
+      <c r="A551" t="s">
+        <v>18</v>
+      </c>
+      <c r="B551">
+        <v>2020</v>
+      </c>
+      <c r="C551">
+        <v>411.605</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3">
+      <c r="A552" t="s">
+        <v>18</v>
+      </c>
+      <c r="B552">
+        <v>2021</v>
+      </c>
+      <c r="C552">
+        <v>155.539</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3">
+      <c r="A553" t="s">
+        <v>18</v>
+      </c>
+      <c r="B553">
+        <v>2022</v>
+      </c>
+      <c r="C553">
+        <v>151.855</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3">
+      <c r="A554" t="s">
+        <v>18</v>
+      </c>
+      <c r="B554">
+        <v>2023</v>
+      </c>
+      <c r="C554">
+        <v>214.405</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3">
+      <c r="A555" t="s">
+        <v>18</v>
+      </c>
+      <c r="B555">
+        <v>2024</v>
+      </c>
+      <c r="C555">
+        <v>286.399</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3">
+      <c r="A556" t="s">
+        <v>18</v>
+      </c>
+      <c r="B556">
+        <v>2025</v>
+      </c>
+      <c r="C556">
+        <v>61.892</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3">
+      <c r="A557" t="s">
         <v>19</v>
       </c>
-      <c r="B433">
+      <c r="B557">
+        <v>1989</v>
+      </c>
+      <c r="C557">
+        <v>165.696</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3">
+      <c r="A558" t="s">
+        <v>19</v>
+      </c>
+      <c r="B558">
+        <v>1990</v>
+      </c>
+      <c r="C558">
+        <v>207.517</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3">
+      <c r="A559" t="s">
+        <v>19</v>
+      </c>
+      <c r="B559">
+        <v>1991</v>
+      </c>
+      <c r="C559">
+        <v>242.225</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3">
+      <c r="A560" t="s">
+        <v>19</v>
+      </c>
+      <c r="B560">
+        <v>1992</v>
+      </c>
+      <c r="C560">
+        <v>1116.246</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3">
+      <c r="A561" t="s">
+        <v>19</v>
+      </c>
+      <c r="B561">
+        <v>1993</v>
+      </c>
+      <c r="C561">
+        <v>148.56</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3">
+      <c r="A562" t="s">
+        <v>19</v>
+      </c>
+      <c r="B562">
+        <v>1994</v>
+      </c>
+      <c r="C562">
+        <v>671.263</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3">
+      <c r="A563" t="s">
+        <v>19</v>
+      </c>
+      <c r="B563">
+        <v>1995</v>
+      </c>
+      <c r="C563">
+        <v>868.654</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3">
+      <c r="A564" t="s">
+        <v>19</v>
+      </c>
+      <c r="B564">
+        <v>1996</v>
+      </c>
+      <c r="C564">
+        <v>966.037</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3">
+      <c r="A565" t="s">
+        <v>19</v>
+      </c>
+      <c r="B565">
+        <v>1997</v>
+      </c>
+      <c r="C565">
+        <v>2194.416</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3">
+      <c r="A566" t="s">
+        <v>19</v>
+      </c>
+      <c r="B566">
+        <v>1998</v>
+      </c>
+      <c r="C566">
+        <v>1882.119</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3">
+      <c r="A567" t="s">
+        <v>19</v>
+      </c>
+      <c r="B567">
+        <v>1999</v>
+      </c>
+      <c r="C567">
+        <v>1622.012</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3">
+      <c r="A568" t="s">
+        <v>19</v>
+      </c>
+      <c r="B568">
+        <v>2000</v>
+      </c>
+      <c r="C568">
+        <v>1075.395</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3">
+      <c r="A569" t="s">
+        <v>19</v>
+      </c>
+      <c r="B569">
+        <v>2001</v>
+      </c>
+      <c r="C569">
+        <v>847.7</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3">
+      <c r="A570" t="s">
+        <v>19</v>
+      </c>
+      <c r="B570">
+        <v>2002</v>
+      </c>
+      <c r="C570">
+        <v>1751.447</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3">
+      <c r="A571" t="s">
+        <v>19</v>
+      </c>
+      <c r="B571">
+        <v>2003</v>
+      </c>
+      <c r="C571">
+        <v>1398.02</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3">
+      <c r="A572" t="s">
+        <v>19</v>
+      </c>
+      <c r="B572">
+        <v>2004</v>
+      </c>
+      <c r="C572">
+        <v>1085.991</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3">
+      <c r="A573" t="s">
+        <v>19</v>
+      </c>
+      <c r="B573">
+        <v>2005</v>
+      </c>
+      <c r="C573">
+        <v>1460.566</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3">
+      <c r="A574" t="s">
+        <v>19</v>
+      </c>
+      <c r="B574">
+        <v>2006</v>
+      </c>
+      <c r="C574">
+        <v>1937.453</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3">
+      <c r="A575" t="s">
+        <v>19</v>
+      </c>
+      <c r="B575">
+        <v>2007</v>
+      </c>
+      <c r="C575">
+        <v>2292.716</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3">
+      <c r="A576" t="s">
+        <v>19</v>
+      </c>
+      <c r="B576">
+        <v>2008</v>
+      </c>
+      <c r="C576">
+        <v>2033.549</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3">
+      <c r="A577" t="s">
+        <v>19</v>
+      </c>
+      <c r="B577">
+        <v>2009</v>
+      </c>
+      <c r="C577">
+        <v>1373.338</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3">
+      <c r="A578" t="s">
+        <v>19</v>
+      </c>
+      <c r="B578">
+        <v>2010</v>
+      </c>
+      <c r="C578">
+        <v>1442.3</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3">
+      <c r="A579" t="s">
+        <v>19</v>
+      </c>
+      <c r="B579">
+        <v>2011</v>
+      </c>
+      <c r="C579">
+        <v>1911.578</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3">
+      <c r="A580" t="s">
+        <v>19</v>
+      </c>
+      <c r="B580">
+        <v>2012</v>
+      </c>
+      <c r="C580">
+        <v>2488.848</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3">
+      <c r="A581" t="s">
+        <v>19</v>
+      </c>
+      <c r="B581">
+        <v>2013</v>
+      </c>
+      <c r="C581">
+        <v>2210.106</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3">
+      <c r="A582" t="s">
+        <v>19</v>
+      </c>
+      <c r="B582">
+        <v>2014</v>
+      </c>
+      <c r="C582">
+        <v>1273.775</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3">
+      <c r="A583" t="s">
+        <v>19</v>
+      </c>
+      <c r="B583">
         <v>2015</v>
       </c>
-      <c r="C433">
-        <v>644</v>
+      <c r="C583">
+        <v>24.05</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3">
+      <c r="A584" t="s">
+        <v>19</v>
+      </c>
+      <c r="B584">
+        <v>2016</v>
+      </c>
+      <c r="C584">
+        <v>186.57</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3">
+      <c r="A585" t="s">
+        <v>19</v>
+      </c>
+      <c r="B585">
+        <v>2017</v>
+      </c>
+      <c r="C585">
+        <v>621.994</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3">
+      <c r="A586" t="s">
+        <v>19</v>
+      </c>
+      <c r="B586">
+        <v>2018</v>
+      </c>
+      <c r="C586">
+        <v>2216.99</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3">
+      <c r="A587" t="s">
+        <v>19</v>
+      </c>
+      <c r="B587">
+        <v>2019</v>
+      </c>
+      <c r="C587">
+        <v>793.841</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3">
+      <c r="A588" t="s">
+        <v>19</v>
+      </c>
+      <c r="B588">
+        <v>2020</v>
+      </c>
+      <c r="C588">
+        <v>411.605</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3">
+      <c r="A589" t="s">
+        <v>19</v>
+      </c>
+      <c r="B589">
+        <v>2021</v>
+      </c>
+      <c r="C589">
+        <v>155.539</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3">
+      <c r="A590" t="s">
+        <v>19</v>
+      </c>
+      <c r="B590">
+        <v>2022</v>
+      </c>
+      <c r="C590">
+        <v>151.855</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3">
+      <c r="A591" t="s">
+        <v>19</v>
+      </c>
+      <c r="B591">
+        <v>2023</v>
+      </c>
+      <c r="C591">
+        <v>214.405</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3">
+      <c r="A592" t="s">
+        <v>19</v>
+      </c>
+      <c r="B592">
+        <v>2024</v>
+      </c>
+      <c r="C592">
+        <v>286.399</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3">
+      <c r="A593" t="s">
+        <v>19</v>
+      </c>
+      <c r="B593">
+        <v>2025</v>
+      </c>
+      <c r="C593">
+        <v>61.892</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/cdat_macarellus_cmsy.xlsx
+++ b/Catch models/cdat_macarellus_cmsy.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="20">
   <si>
     <t>Stock</t>
   </si>
@@ -416,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D593"/>
+  <dimension ref="A1:D561"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1">
@@ -441,7 +441,7 @@
         <v>1989</v>
       </c>
       <c r="C2">
-        <v>165.696</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -452,7 +452,7 @@
         <v>1990</v>
       </c>
       <c r="C3">
-        <v>207.517</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -463,7 +463,7 @@
         <v>1991</v>
       </c>
       <c r="C4">
-        <v>242.225</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -474,7 +474,7 @@
         <v>1992</v>
       </c>
       <c r="C5">
-        <v>1116.246</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -485,7 +485,7 @@
         <v>1993</v>
       </c>
       <c r="C6">
-        <v>148.56</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -496,7 +496,7 @@
         <v>1994</v>
       </c>
       <c r="C7">
-        <v>671.263</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -507,7 +507,7 @@
         <v>1995</v>
       </c>
       <c r="C8">
-        <v>868.654</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -518,7 +518,7 @@
         <v>1996</v>
       </c>
       <c r="C9">
-        <v>966.037</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -529,7 +529,7 @@
         <v>1997</v>
       </c>
       <c r="C10">
-        <v>2194.416</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -540,7 +540,7 @@
         <v>1998</v>
       </c>
       <c r="C11">
-        <v>1882.119</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -551,7 +551,7 @@
         <v>1999</v>
       </c>
       <c r="C12">
-        <v>1622.012</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -562,7 +562,7 @@
         <v>2000</v>
       </c>
       <c r="C13">
-        <v>1075.395</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -573,7 +573,7 @@
         <v>2001</v>
       </c>
       <c r="C14">
-        <v>847.7</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -584,7 +584,7 @@
         <v>2002</v>
       </c>
       <c r="C15">
-        <v>1751.447</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -595,7 +595,7 @@
         <v>2003</v>
       </c>
       <c r="C16">
-        <v>1398.02</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -606,7 +606,7 @@
         <v>2004</v>
       </c>
       <c r="C17">
-        <v>1085.991</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -617,7 +617,7 @@
         <v>2005</v>
       </c>
       <c r="C18">
-        <v>1460.566</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -628,7 +628,7 @@
         <v>2006</v>
       </c>
       <c r="C19">
-        <v>1937.453</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -639,7 +639,7 @@
         <v>2007</v>
       </c>
       <c r="C20">
-        <v>2292.716</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -650,7 +650,7 @@
         <v>2008</v>
       </c>
       <c r="C21">
-        <v>2033.549</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -661,7 +661,7 @@
         <v>2009</v>
       </c>
       <c r="C22">
-        <v>1373.338</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -672,7 +672,7 @@
         <v>2010</v>
       </c>
       <c r="C23">
-        <v>1442.3</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -683,7 +683,7 @@
         <v>2011</v>
       </c>
       <c r="C24">
-        <v>1911.578</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -694,7 +694,7 @@
         <v>2012</v>
       </c>
       <c r="C25">
-        <v>2488.848</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -705,7 +705,7 @@
         <v>2013</v>
       </c>
       <c r="C26">
-        <v>2210.106</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -716,7 +716,7 @@
         <v>2014</v>
       </c>
       <c r="C27">
-        <v>1273.775</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -727,7 +727,7 @@
         <v>2015</v>
       </c>
       <c r="C28">
-        <v>24.05</v>
+        <v>644</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -738,7 +738,7 @@
         <v>2016</v>
       </c>
       <c r="C29">
-        <v>186.57</v>
+        <v>650</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -749,7 +749,7 @@
         <v>2017</v>
       </c>
       <c r="C30">
-        <v>621.994</v>
+        <v>657</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -760,7 +760,7 @@
         <v>2018</v>
       </c>
       <c r="C31">
-        <v>2216.99</v>
+        <v>554.5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -771,7 +771,7 @@
         <v>2019</v>
       </c>
       <c r="C32">
-        <v>793.841</v>
+        <v>806</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -782,7 +782,7 @@
         <v>2020</v>
       </c>
       <c r="C33">
-        <v>411.605</v>
+        <v>410</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -793,7 +793,7 @@
         <v>2021</v>
       </c>
       <c r="C34">
-        <v>155.539</v>
+        <v>160</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -804,7 +804,7 @@
         <v>2022</v>
       </c>
       <c r="C35">
-        <v>151.855</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -815,29 +815,29 @@
         <v>2023</v>
       </c>
       <c r="C36">
-        <v>214.405</v>
+        <v>248</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B37">
-        <v>2024</v>
+        <v>1989</v>
       </c>
       <c r="C37">
-        <v>286.399</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B38">
-        <v>2025</v>
+        <v>1990</v>
       </c>
       <c r="C38">
-        <v>61.892</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -845,10 +845,10 @@
         <v>5</v>
       </c>
       <c r="B39">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="C39">
-        <v>165.696</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -856,10 +856,10 @@
         <v>5</v>
       </c>
       <c r="B40">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="C40">
-        <v>207.517</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -867,10 +867,10 @@
         <v>5</v>
       </c>
       <c r="B41">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="C41">
-        <v>242.225</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -878,10 +878,10 @@
         <v>5</v>
       </c>
       <c r="B42">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="C42">
-        <v>1116.246</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -889,10 +889,10 @@
         <v>5</v>
       </c>
       <c r="B43">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="C43">
-        <v>148.56</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -900,10 +900,10 @@
         <v>5</v>
       </c>
       <c r="B44">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="C44">
-        <v>671.263</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -911,10 +911,10 @@
         <v>5</v>
       </c>
       <c r="B45">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="C45">
-        <v>868.654</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -922,10 +922,10 @@
         <v>5</v>
       </c>
       <c r="B46">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="C46">
-        <v>966.037</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -933,10 +933,10 @@
         <v>5</v>
       </c>
       <c r="B47">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="C47">
-        <v>2194.416</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -944,10 +944,10 @@
         <v>5</v>
       </c>
       <c r="B48">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="C48">
-        <v>1882.119</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -955,10 +955,10 @@
         <v>5</v>
       </c>
       <c r="B49">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="C49">
-        <v>1622.012</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -966,10 +966,10 @@
         <v>5</v>
       </c>
       <c r="B50">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="C50">
-        <v>1075.395</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -977,10 +977,10 @@
         <v>5</v>
       </c>
       <c r="B51">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="C51">
-        <v>847.7</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -988,10 +988,10 @@
         <v>5</v>
       </c>
       <c r="B52">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="C52">
-        <v>1751.447</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -999,10 +999,10 @@
         <v>5</v>
       </c>
       <c r="B53">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="C53">
-        <v>1398.02</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1010,10 +1010,10 @@
         <v>5</v>
       </c>
       <c r="B54">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="C54">
-        <v>1085.991</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1021,10 +1021,10 @@
         <v>5</v>
       </c>
       <c r="B55">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="C55">
-        <v>1460.566</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1032,10 +1032,10 @@
         <v>5</v>
       </c>
       <c r="B56">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="C56">
-        <v>1937.453</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1043,10 +1043,10 @@
         <v>5</v>
       </c>
       <c r="B57">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="C57">
-        <v>2292.716</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1054,10 +1054,10 @@
         <v>5</v>
       </c>
       <c r="B58">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="C58">
-        <v>2033.549</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1065,10 +1065,10 @@
         <v>5</v>
       </c>
       <c r="B59">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="C59">
-        <v>1373.338</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1076,10 +1076,10 @@
         <v>5</v>
       </c>
       <c r="B60">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C60">
-        <v>1442.3</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1087,10 +1087,10 @@
         <v>5</v>
       </c>
       <c r="B61">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="C61">
-        <v>1911.578</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1098,10 +1098,10 @@
         <v>5</v>
       </c>
       <c r="B62">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C62">
-        <v>2488.848</v>
+        <v>151</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1109,10 +1109,10 @@
         <v>5</v>
       </c>
       <c r="B63">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="C63">
-        <v>2210.106</v>
+        <v>644</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1120,10 +1120,10 @@
         <v>5</v>
       </c>
       <c r="B64">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C64">
-        <v>1273.775</v>
+        <v>650</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1131,10 +1131,10 @@
         <v>5</v>
       </c>
       <c r="B65">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="C65">
-        <v>24.05</v>
+        <v>657</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1142,10 +1142,10 @@
         <v>5</v>
       </c>
       <c r="B66">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C66">
-        <v>186.57</v>
+        <v>554.5</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1153,10 +1153,10 @@
         <v>5</v>
       </c>
       <c r="B67">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C67">
-        <v>621.994</v>
+        <v>806</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1164,10 +1164,10 @@
         <v>5</v>
       </c>
       <c r="B68">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C68">
-        <v>2216.99</v>
+        <v>410</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1175,10 +1175,10 @@
         <v>5</v>
       </c>
       <c r="B69">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C69">
-        <v>793.841</v>
+        <v>160</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1186,10 +1186,10 @@
         <v>5</v>
       </c>
       <c r="B70">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C70">
-        <v>411.605</v>
+        <v>176</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1197,54 +1197,54 @@
         <v>5</v>
       </c>
       <c r="B71">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="C71">
-        <v>155.539</v>
+        <v>248</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B72">
-        <v>2022</v>
+        <v>1989</v>
       </c>
       <c r="C72">
-        <v>151.855</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B73">
-        <v>2023</v>
+        <v>1990</v>
       </c>
       <c r="C73">
-        <v>214.405</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B74">
-        <v>2024</v>
+        <v>1991</v>
       </c>
       <c r="C74">
-        <v>286.399</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B75">
-        <v>2025</v>
+        <v>1992</v>
       </c>
       <c r="C75">
-        <v>61.892</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1252,10 +1252,10 @@
         <v>6</v>
       </c>
       <c r="B76">
-        <v>1989</v>
+        <v>1993</v>
       </c>
       <c r="C76">
-        <v>165.696</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1263,10 +1263,10 @@
         <v>6</v>
       </c>
       <c r="B77">
-        <v>1990</v>
+        <v>1994</v>
       </c>
       <c r="C77">
-        <v>207.517</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1274,10 +1274,10 @@
         <v>6</v>
       </c>
       <c r="B78">
-        <v>1991</v>
+        <v>1995</v>
       </c>
       <c r="C78">
-        <v>242.225</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1285,10 +1285,10 @@
         <v>6</v>
       </c>
       <c r="B79">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="C79">
-        <v>1116.246</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1296,10 +1296,10 @@
         <v>6</v>
       </c>
       <c r="B80">
-        <v>1993</v>
+        <v>1997</v>
       </c>
       <c r="C80">
-        <v>148.56</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1307,10 +1307,10 @@
         <v>6</v>
       </c>
       <c r="B81">
-        <v>1994</v>
+        <v>1998</v>
       </c>
       <c r="C81">
-        <v>671.263</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1318,10 +1318,10 @@
         <v>6</v>
       </c>
       <c r="B82">
-        <v>1995</v>
+        <v>1999</v>
       </c>
       <c r="C82">
-        <v>868.654</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1329,10 +1329,10 @@
         <v>6</v>
       </c>
       <c r="B83">
-        <v>1996</v>
+        <v>2000</v>
       </c>
       <c r="C83">
-        <v>966.037</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1340,10 +1340,10 @@
         <v>6</v>
       </c>
       <c r="B84">
-        <v>1997</v>
+        <v>2001</v>
       </c>
       <c r="C84">
-        <v>2194.416</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1351,10 +1351,10 @@
         <v>6</v>
       </c>
       <c r="B85">
-        <v>1998</v>
+        <v>2002</v>
       </c>
       <c r="C85">
-        <v>1882.119</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1362,10 +1362,10 @@
         <v>6</v>
       </c>
       <c r="B86">
-        <v>1999</v>
+        <v>2003</v>
       </c>
       <c r="C86">
-        <v>1622.012</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1373,10 +1373,10 @@
         <v>6</v>
       </c>
       <c r="B87">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="C87">
-        <v>1075.395</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1384,10 +1384,10 @@
         <v>6</v>
       </c>
       <c r="B88">
-        <v>2001</v>
+        <v>2005</v>
       </c>
       <c r="C88">
-        <v>847.7</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1395,10 +1395,10 @@
         <v>6</v>
       </c>
       <c r="B89">
-        <v>2002</v>
+        <v>2006</v>
       </c>
       <c r="C89">
-        <v>1751.447</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1406,10 +1406,10 @@
         <v>6</v>
       </c>
       <c r="B90">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="C90">
-        <v>1398.02</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1417,10 +1417,10 @@
         <v>6</v>
       </c>
       <c r="B91">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="C91">
-        <v>1085.991</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1428,10 +1428,10 @@
         <v>6</v>
       </c>
       <c r="B92">
-        <v>2005</v>
+        <v>2009</v>
       </c>
       <c r="C92">
-        <v>1460.566</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1439,10 +1439,10 @@
         <v>6</v>
       </c>
       <c r="B93">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="C93">
-        <v>1937.453</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1450,10 +1450,10 @@
         <v>6</v>
       </c>
       <c r="B94">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="C94">
-        <v>2292.716</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1461,10 +1461,10 @@
         <v>6</v>
       </c>
       <c r="B95">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="C95">
-        <v>2033.549</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1472,10 +1472,10 @@
         <v>6</v>
       </c>
       <c r="B96">
-        <v>2009</v>
+        <v>2013</v>
       </c>
       <c r="C96">
-        <v>1373.338</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1483,10 +1483,10 @@
         <v>6</v>
       </c>
       <c r="B97">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C97">
-        <v>1442.3</v>
+        <v>151</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1494,10 +1494,10 @@
         <v>6</v>
       </c>
       <c r="B98">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="C98">
-        <v>1911.578</v>
+        <v>644</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1505,10 +1505,10 @@
         <v>6</v>
       </c>
       <c r="B99">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C99">
-        <v>2488.848</v>
+        <v>650</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1516,10 +1516,10 @@
         <v>6</v>
       </c>
       <c r="B100">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="C100">
-        <v>2210.106</v>
+        <v>657</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -1527,10 +1527,10 @@
         <v>6</v>
       </c>
       <c r="B101">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="C101">
-        <v>1273.775</v>
+        <v>554.5</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -1538,10 +1538,10 @@
         <v>6</v>
       </c>
       <c r="B102">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="C102">
-        <v>24.05</v>
+        <v>806</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -1549,10 +1549,10 @@
         <v>6</v>
       </c>
       <c r="B103">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C103">
-        <v>186.57</v>
+        <v>410</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -1560,10 +1560,10 @@
         <v>6</v>
       </c>
       <c r="B104">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C104">
-        <v>621.994</v>
+        <v>160</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -1571,10 +1571,10 @@
         <v>6</v>
       </c>
       <c r="B105">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C105">
-        <v>2216.99</v>
+        <v>176</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -1582,76 +1582,76 @@
         <v>6</v>
       </c>
       <c r="B106">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="C106">
-        <v>793.841</v>
+        <v>248</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B107">
-        <v>2020</v>
+        <v>1989</v>
       </c>
       <c r="C107">
-        <v>411.605</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B108">
-        <v>2021</v>
+        <v>1990</v>
       </c>
       <c r="C108">
-        <v>155.539</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B109">
-        <v>2022</v>
+        <v>1991</v>
       </c>
       <c r="C109">
-        <v>151.855</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B110">
-        <v>2023</v>
+        <v>1992</v>
       </c>
       <c r="C110">
-        <v>214.405</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B111">
-        <v>2024</v>
+        <v>1993</v>
       </c>
       <c r="C111">
-        <v>286.399</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B112">
-        <v>2025</v>
+        <v>1994</v>
       </c>
       <c r="C112">
-        <v>61.892</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -1659,10 +1659,10 @@
         <v>7</v>
       </c>
       <c r="B113">
-        <v>1989</v>
+        <v>1995</v>
       </c>
       <c r="C113">
-        <v>165.696</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -1670,10 +1670,10 @@
         <v>7</v>
       </c>
       <c r="B114">
-        <v>1990</v>
+        <v>1996</v>
       </c>
       <c r="C114">
-        <v>207.517</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -1681,10 +1681,10 @@
         <v>7</v>
       </c>
       <c r="B115">
-        <v>1991</v>
+        <v>1997</v>
       </c>
       <c r="C115">
-        <v>242.225</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -1692,10 +1692,10 @@
         <v>7</v>
       </c>
       <c r="B116">
-        <v>1992</v>
+        <v>1998</v>
       </c>
       <c r="C116">
-        <v>1116.246</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -1703,10 +1703,10 @@
         <v>7</v>
       </c>
       <c r="B117">
-        <v>1993</v>
+        <v>1999</v>
       </c>
       <c r="C117">
-        <v>148.56</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -1714,10 +1714,10 @@
         <v>7</v>
       </c>
       <c r="B118">
-        <v>1994</v>
+        <v>2000</v>
       </c>
       <c r="C118">
-        <v>671.263</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -1725,10 +1725,10 @@
         <v>7</v>
       </c>
       <c r="B119">
-        <v>1995</v>
+        <v>2001</v>
       </c>
       <c r="C119">
-        <v>868.654</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -1736,10 +1736,10 @@
         <v>7</v>
       </c>
       <c r="B120">
-        <v>1996</v>
+        <v>2002</v>
       </c>
       <c r="C120">
-        <v>966.037</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -1747,10 +1747,10 @@
         <v>7</v>
       </c>
       <c r="B121">
-        <v>1997</v>
+        <v>2003</v>
       </c>
       <c r="C121">
-        <v>2194.416</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -1758,10 +1758,10 @@
         <v>7</v>
       </c>
       <c r="B122">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="C122">
-        <v>1882.119</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -1769,10 +1769,10 @@
         <v>7</v>
       </c>
       <c r="B123">
-        <v>1999</v>
+        <v>2005</v>
       </c>
       <c r="C123">
-        <v>1622.012</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -1780,10 +1780,10 @@
         <v>7</v>
       </c>
       <c r="B124">
-        <v>2000</v>
+        <v>2006</v>
       </c>
       <c r="C124">
-        <v>1075.395</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -1791,10 +1791,10 @@
         <v>7</v>
       </c>
       <c r="B125">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="C125">
-        <v>847.7</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -1802,10 +1802,10 @@
         <v>7</v>
       </c>
       <c r="B126">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="C126">
-        <v>1751.447</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -1813,10 +1813,10 @@
         <v>7</v>
       </c>
       <c r="B127">
-        <v>2003</v>
+        <v>2009</v>
       </c>
       <c r="C127">
-        <v>1398.02</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -1824,10 +1824,10 @@
         <v>7</v>
       </c>
       <c r="B128">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="C128">
-        <v>1085.991</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -1835,10 +1835,10 @@
         <v>7</v>
       </c>
       <c r="B129">
-        <v>2005</v>
+        <v>2011</v>
       </c>
       <c r="C129">
-        <v>1460.566</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -1846,10 +1846,10 @@
         <v>7</v>
       </c>
       <c r="B130">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="C130">
-        <v>1937.453</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -1857,10 +1857,10 @@
         <v>7</v>
       </c>
       <c r="B131">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="C131">
-        <v>2292.716</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -1868,10 +1868,10 @@
         <v>7</v>
       </c>
       <c r="B132">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C132">
-        <v>2033.549</v>
+        <v>151</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -1879,10 +1879,10 @@
         <v>7</v>
       </c>
       <c r="B133">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="C133">
-        <v>1373.338</v>
+        <v>644</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -1890,10 +1890,10 @@
         <v>7</v>
       </c>
       <c r="B134">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C134">
-        <v>1442.3</v>
+        <v>650</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -1901,10 +1901,10 @@
         <v>7</v>
       </c>
       <c r="B135">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="C135">
-        <v>1911.578</v>
+        <v>657</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -1912,10 +1912,10 @@
         <v>7</v>
       </c>
       <c r="B136">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C136">
-        <v>2488.848</v>
+        <v>554.5</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -1923,10 +1923,10 @@
         <v>7</v>
       </c>
       <c r="B137">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="C137">
-        <v>2210.106</v>
+        <v>806</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -1934,10 +1934,10 @@
         <v>7</v>
       </c>
       <c r="B138">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="C138">
-        <v>1273.775</v>
+        <v>410</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -1945,10 +1945,10 @@
         <v>7</v>
       </c>
       <c r="B139">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="C139">
-        <v>24.05</v>
+        <v>160</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -1956,10 +1956,10 @@
         <v>7</v>
       </c>
       <c r="B140">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C140">
-        <v>186.57</v>
+        <v>176</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -1967,98 +1967,98 @@
         <v>7</v>
       </c>
       <c r="B141">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="C141">
-        <v>621.994</v>
+        <v>248</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B142">
-        <v>2018</v>
+        <v>1989</v>
       </c>
       <c r="C142">
-        <v>2216.99</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B143">
-        <v>2019</v>
+        <v>1990</v>
       </c>
       <c r="C143">
-        <v>793.841</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B144">
-        <v>2020</v>
+        <v>1991</v>
       </c>
       <c r="C144">
-        <v>411.605</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B145">
-        <v>2021</v>
+        <v>1992</v>
       </c>
       <c r="C145">
-        <v>155.539</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B146">
-        <v>2022</v>
+        <v>1993</v>
       </c>
       <c r="C146">
-        <v>151.855</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B147">
-        <v>2023</v>
+        <v>1994</v>
       </c>
       <c r="C147">
-        <v>214.405</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B148">
-        <v>2024</v>
+        <v>1995</v>
       </c>
       <c r="C148">
-        <v>286.399</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B149">
-        <v>2025</v>
+        <v>1996</v>
       </c>
       <c r="C149">
-        <v>61.892</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -2066,10 +2066,10 @@
         <v>8</v>
       </c>
       <c r="B150">
-        <v>1989</v>
+        <v>1997</v>
       </c>
       <c r="C150">
-        <v>165.696</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -2077,10 +2077,10 @@
         <v>8</v>
       </c>
       <c r="B151">
-        <v>1990</v>
+        <v>1998</v>
       </c>
       <c r="C151">
-        <v>207.517</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -2088,10 +2088,10 @@
         <v>8</v>
       </c>
       <c r="B152">
-        <v>1991</v>
+        <v>1999</v>
       </c>
       <c r="C152">
-        <v>242.225</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -2099,10 +2099,10 @@
         <v>8</v>
       </c>
       <c r="B153">
-        <v>1992</v>
+        <v>2000</v>
       </c>
       <c r="C153">
-        <v>1116.246</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -2110,10 +2110,10 @@
         <v>8</v>
       </c>
       <c r="B154">
-        <v>1993</v>
+        <v>2001</v>
       </c>
       <c r="C154">
-        <v>148.56</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -2121,10 +2121,10 @@
         <v>8</v>
       </c>
       <c r="B155">
-        <v>1994</v>
+        <v>2002</v>
       </c>
       <c r="C155">
-        <v>671.263</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -2132,10 +2132,10 @@
         <v>8</v>
       </c>
       <c r="B156">
-        <v>1995</v>
+        <v>2003</v>
       </c>
       <c r="C156">
-        <v>868.654</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -2143,10 +2143,10 @@
         <v>8</v>
       </c>
       <c r="B157">
-        <v>1996</v>
+        <v>2004</v>
       </c>
       <c r="C157">
-        <v>966.037</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -2154,10 +2154,10 @@
         <v>8</v>
       </c>
       <c r="B158">
-        <v>1997</v>
+        <v>2005</v>
       </c>
       <c r="C158">
-        <v>2194.416</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -2165,10 +2165,10 @@
         <v>8</v>
       </c>
       <c r="B159">
-        <v>1998</v>
+        <v>2006</v>
       </c>
       <c r="C159">
-        <v>1882.119</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -2176,10 +2176,10 @@
         <v>8</v>
       </c>
       <c r="B160">
-        <v>1999</v>
+        <v>2007</v>
       </c>
       <c r="C160">
-        <v>1622.012</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -2187,10 +2187,10 @@
         <v>8</v>
       </c>
       <c r="B161">
-        <v>2000</v>
+        <v>2008</v>
       </c>
       <c r="C161">
-        <v>1075.395</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -2198,10 +2198,10 @@
         <v>8</v>
       </c>
       <c r="B162">
-        <v>2001</v>
+        <v>2009</v>
       </c>
       <c r="C162">
-        <v>847.7</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -2209,10 +2209,10 @@
         <v>8</v>
       </c>
       <c r="B163">
-        <v>2002</v>
+        <v>2010</v>
       </c>
       <c r="C163">
-        <v>1751.447</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -2220,10 +2220,10 @@
         <v>8</v>
       </c>
       <c r="B164">
-        <v>2003</v>
+        <v>2011</v>
       </c>
       <c r="C164">
-        <v>1398.02</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -2231,10 +2231,10 @@
         <v>8</v>
       </c>
       <c r="B165">
-        <v>2004</v>
+        <v>2012</v>
       </c>
       <c r="C165">
-        <v>1085.991</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -2242,10 +2242,10 @@
         <v>8</v>
       </c>
       <c r="B166">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="C166">
-        <v>1460.566</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -2253,10 +2253,10 @@
         <v>8</v>
       </c>
       <c r="B167">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C167">
-        <v>1937.453</v>
+        <v>151</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -2264,10 +2264,10 @@
         <v>8</v>
       </c>
       <c r="B168">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="C168">
-        <v>2292.716</v>
+        <v>644</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -2275,10 +2275,10 @@
         <v>8</v>
       </c>
       <c r="B169">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C169">
-        <v>2033.549</v>
+        <v>650</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -2286,10 +2286,10 @@
         <v>8</v>
       </c>
       <c r="B170">
-        <v>2009</v>
+        <v>2017</v>
       </c>
       <c r="C170">
-        <v>1373.338</v>
+        <v>657</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -2297,10 +2297,10 @@
         <v>8</v>
       </c>
       <c r="B171">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C171">
-        <v>1442.3</v>
+        <v>554.5</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -2308,10 +2308,10 @@
         <v>8</v>
       </c>
       <c r="B172">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C172">
-        <v>1911.578</v>
+        <v>806</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -2319,10 +2319,10 @@
         <v>8</v>
       </c>
       <c r="B173">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C173">
-        <v>2488.848</v>
+        <v>410</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -2330,10 +2330,10 @@
         <v>8</v>
       </c>
       <c r="B174">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="C174">
-        <v>2210.106</v>
+        <v>160</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -2341,10 +2341,10 @@
         <v>8</v>
       </c>
       <c r="B175">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C175">
-        <v>1273.775</v>
+        <v>176</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -2352,120 +2352,120 @@
         <v>8</v>
       </c>
       <c r="B176">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="C176">
-        <v>24.05</v>
+        <v>248</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B177">
-        <v>2016</v>
+        <v>1989</v>
       </c>
       <c r="C177">
-        <v>186.57</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B178">
-        <v>2017</v>
+        <v>1990</v>
       </c>
       <c r="C178">
-        <v>621.994</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B179">
-        <v>2018</v>
+        <v>1991</v>
       </c>
       <c r="C179">
-        <v>2216.99</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B180">
-        <v>2019</v>
+        <v>1992</v>
       </c>
       <c r="C180">
-        <v>793.841</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B181">
-        <v>2020</v>
+        <v>1993</v>
       </c>
       <c r="C181">
-        <v>411.605</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B182">
-        <v>2021</v>
+        <v>1994</v>
       </c>
       <c r="C182">
-        <v>155.539</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B183">
-        <v>2022</v>
+        <v>1995</v>
       </c>
       <c r="C183">
-        <v>151.855</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B184">
-        <v>2023</v>
+        <v>1996</v>
       </c>
       <c r="C184">
-        <v>214.405</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B185">
-        <v>2024</v>
+        <v>1997</v>
       </c>
       <c r="C185">
-        <v>286.399</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B186">
-        <v>2025</v>
+        <v>1998</v>
       </c>
       <c r="C186">
-        <v>61.892</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -2473,10 +2473,10 @@
         <v>9</v>
       </c>
       <c r="B187">
-        <v>1989</v>
+        <v>1999</v>
       </c>
       <c r="C187">
-        <v>165.696</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -2484,10 +2484,10 @@
         <v>9</v>
       </c>
       <c r="B188">
-        <v>1990</v>
+        <v>2000</v>
       </c>
       <c r="C188">
-        <v>207.517</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -2495,10 +2495,10 @@
         <v>9</v>
       </c>
       <c r="B189">
-        <v>1991</v>
+        <v>2001</v>
       </c>
       <c r="C189">
-        <v>242.225</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -2506,10 +2506,10 @@
         <v>9</v>
       </c>
       <c r="B190">
-        <v>1992</v>
+        <v>2002</v>
       </c>
       <c r="C190">
-        <v>1116.246</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -2517,10 +2517,10 @@
         <v>9</v>
       </c>
       <c r="B191">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="C191">
-        <v>148.56</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -2528,10 +2528,10 @@
         <v>9</v>
       </c>
       <c r="B192">
-        <v>1994</v>
+        <v>2004</v>
       </c>
       <c r="C192">
-        <v>671.263</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -2539,10 +2539,10 @@
         <v>9</v>
       </c>
       <c r="B193">
-        <v>1995</v>
+        <v>2005</v>
       </c>
       <c r="C193">
-        <v>868.654</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -2550,10 +2550,10 @@
         <v>9</v>
       </c>
       <c r="B194">
-        <v>1996</v>
+        <v>2006</v>
       </c>
       <c r="C194">
-        <v>966.037</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -2561,10 +2561,10 @@
         <v>9</v>
       </c>
       <c r="B195">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="C195">
-        <v>2194.416</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -2572,10 +2572,10 @@
         <v>9</v>
       </c>
       <c r="B196">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="C196">
-        <v>1882.119</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -2583,10 +2583,10 @@
         <v>9</v>
       </c>
       <c r="B197">
-        <v>1999</v>
+        <v>2009</v>
       </c>
       <c r="C197">
-        <v>1622.012</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -2594,10 +2594,10 @@
         <v>9</v>
       </c>
       <c r="B198">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="C198">
-        <v>1075.395</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -2605,10 +2605,10 @@
         <v>9</v>
       </c>
       <c r="B199">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="C199">
-        <v>847.7</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -2616,10 +2616,10 @@
         <v>9</v>
       </c>
       <c r="B200">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="C200">
-        <v>1751.447</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -2627,10 +2627,10 @@
         <v>9</v>
       </c>
       <c r="B201">
-        <v>2003</v>
+        <v>2013</v>
       </c>
       <c r="C201">
-        <v>1398.02</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -2638,10 +2638,10 @@
         <v>9</v>
       </c>
       <c r="B202">
-        <v>2004</v>
+        <v>2014</v>
       </c>
       <c r="C202">
-        <v>1085.991</v>
+        <v>151</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -2649,10 +2649,10 @@
         <v>9</v>
       </c>
       <c r="B203">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="C203">
-        <v>1460.566</v>
+        <v>644</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -2660,10 +2660,10 @@
         <v>9</v>
       </c>
       <c r="B204">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C204">
-        <v>1937.453</v>
+        <v>650</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -2671,10 +2671,10 @@
         <v>9</v>
       </c>
       <c r="B205">
-        <v>2007</v>
+        <v>2017</v>
       </c>
       <c r="C205">
-        <v>2292.716</v>
+        <v>657</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -2682,10 +2682,10 @@
         <v>9</v>
       </c>
       <c r="B206">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="C206">
-        <v>2033.549</v>
+        <v>554.5</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -2693,10 +2693,10 @@
         <v>9</v>
       </c>
       <c r="B207">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="C207">
-        <v>1373.338</v>
+        <v>806</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -2704,10 +2704,10 @@
         <v>9</v>
       </c>
       <c r="B208">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="C208">
-        <v>1442.3</v>
+        <v>410</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -2715,10 +2715,10 @@
         <v>9</v>
       </c>
       <c r="B209">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="C209">
-        <v>1911.578</v>
+        <v>160</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -2726,10 +2726,10 @@
         <v>9</v>
       </c>
       <c r="B210">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C210">
-        <v>2488.848</v>
+        <v>176</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -2737,142 +2737,142 @@
         <v>9</v>
       </c>
       <c r="B211">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="C211">
-        <v>2210.106</v>
+        <v>248</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B212">
-        <v>2014</v>
+        <v>1989</v>
       </c>
       <c r="C212">
-        <v>1273.775</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B213">
-        <v>2015</v>
+        <v>1990</v>
       </c>
       <c r="C213">
-        <v>24.05</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B214">
-        <v>2016</v>
+        <v>1991</v>
       </c>
       <c r="C214">
-        <v>186.57</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B215">
-        <v>2017</v>
+        <v>1992</v>
       </c>
       <c r="C215">
-        <v>621.994</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B216">
-        <v>2018</v>
+        <v>1993</v>
       </c>
       <c r="C216">
-        <v>2216.99</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B217">
-        <v>2019</v>
+        <v>1994</v>
       </c>
       <c r="C217">
-        <v>793.841</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B218">
-        <v>2020</v>
+        <v>1995</v>
       </c>
       <c r="C218">
-        <v>411.605</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B219">
-        <v>2021</v>
+        <v>1996</v>
       </c>
       <c r="C219">
-        <v>155.539</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B220">
-        <v>2022</v>
+        <v>1997</v>
       </c>
       <c r="C220">
-        <v>151.855</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B221">
-        <v>2023</v>
+        <v>1998</v>
       </c>
       <c r="C221">
-        <v>214.405</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B222">
-        <v>2024</v>
+        <v>1999</v>
       </c>
       <c r="C222">
-        <v>286.399</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B223">
-        <v>2025</v>
+        <v>2000</v>
       </c>
       <c r="C223">
-        <v>61.892</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -2880,10 +2880,10 @@
         <v>10</v>
       </c>
       <c r="B224">
-        <v>1989</v>
+        <v>2001</v>
       </c>
       <c r="C224">
-        <v>165.696</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -2891,10 +2891,10 @@
         <v>10</v>
       </c>
       <c r="B225">
-        <v>1990</v>
+        <v>2002</v>
       </c>
       <c r="C225">
-        <v>207.517</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -2902,10 +2902,10 @@
         <v>10</v>
       </c>
       <c r="B226">
-        <v>1991</v>
+        <v>2003</v>
       </c>
       <c r="C226">
-        <v>242.225</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -2913,10 +2913,10 @@
         <v>10</v>
       </c>
       <c r="B227">
-        <v>1992</v>
+        <v>2004</v>
       </c>
       <c r="C227">
-        <v>1116.246</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -2924,10 +2924,10 @@
         <v>10</v>
       </c>
       <c r="B228">
-        <v>1993</v>
+        <v>2005</v>
       </c>
       <c r="C228">
-        <v>148.56</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -2935,10 +2935,10 @@
         <v>10</v>
       </c>
       <c r="B229">
-        <v>1994</v>
+        <v>2006</v>
       </c>
       <c r="C229">
-        <v>671.263</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -2946,10 +2946,10 @@
         <v>10</v>
       </c>
       <c r="B230">
-        <v>1995</v>
+        <v>2007</v>
       </c>
       <c r="C230">
-        <v>868.654</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -2957,10 +2957,10 @@
         <v>10</v>
       </c>
       <c r="B231">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="C231">
-        <v>966.037</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -2968,10 +2968,10 @@
         <v>10</v>
       </c>
       <c r="B232">
-        <v>1997</v>
+        <v>2009</v>
       </c>
       <c r="C232">
-        <v>2194.416</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -2979,10 +2979,10 @@
         <v>10</v>
       </c>
       <c r="B233">
-        <v>1998</v>
+        <v>2010</v>
       </c>
       <c r="C233">
-        <v>1882.119</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -2990,10 +2990,10 @@
         <v>10</v>
       </c>
       <c r="B234">
-        <v>1999</v>
+        <v>2011</v>
       </c>
       <c r="C234">
-        <v>1622.012</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -3001,10 +3001,10 @@
         <v>10</v>
       </c>
       <c r="B235">
-        <v>2000</v>
+        <v>2012</v>
       </c>
       <c r="C235">
-        <v>1075.395</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -3012,10 +3012,10 @@
         <v>10</v>
       </c>
       <c r="B236">
-        <v>2001</v>
+        <v>2013</v>
       </c>
       <c r="C236">
-        <v>847.7</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -3023,10 +3023,10 @@
         <v>10</v>
       </c>
       <c r="B237">
-        <v>2002</v>
+        <v>2014</v>
       </c>
       <c r="C237">
-        <v>1751.447</v>
+        <v>151</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -3034,10 +3034,10 @@
         <v>10</v>
       </c>
       <c r="B238">
-        <v>2003</v>
+        <v>2015</v>
       </c>
       <c r="C238">
-        <v>1398.02</v>
+        <v>644</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -3045,10 +3045,10 @@
         <v>10</v>
       </c>
       <c r="B239">
-        <v>2004</v>
+        <v>2016</v>
       </c>
       <c r="C239">
-        <v>1085.991</v>
+        <v>650</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -3056,10 +3056,10 @@
         <v>10</v>
       </c>
       <c r="B240">
-        <v>2005</v>
+        <v>2017</v>
       </c>
       <c r="C240">
-        <v>1460.566</v>
+        <v>657</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -3067,10 +3067,10 @@
         <v>10</v>
       </c>
       <c r="B241">
-        <v>2006</v>
+        <v>2018</v>
       </c>
       <c r="C241">
-        <v>1937.453</v>
+        <v>554.5</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -3078,10 +3078,10 @@
         <v>10</v>
       </c>
       <c r="B242">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="C242">
-        <v>2292.716</v>
+        <v>806</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -3089,10 +3089,10 @@
         <v>10</v>
       </c>
       <c r="B243">
-        <v>2008</v>
+        <v>2020</v>
       </c>
       <c r="C243">
-        <v>2033.549</v>
+        <v>410</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -3100,10 +3100,10 @@
         <v>10</v>
       </c>
       <c r="B244">
-        <v>2009</v>
+        <v>2021</v>
       </c>
       <c r="C244">
-        <v>1373.338</v>
+        <v>160</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -3111,10 +3111,10 @@
         <v>10</v>
       </c>
       <c r="B245">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C245">
-        <v>1442.3</v>
+        <v>176</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -3122,164 +3122,164 @@
         <v>10</v>
       </c>
       <c r="B246">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="C246">
-        <v>1911.578</v>
+        <v>248</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B247">
-        <v>2012</v>
+        <v>1989</v>
       </c>
       <c r="C247">
-        <v>2488.848</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B248">
-        <v>2013</v>
+        <v>1990</v>
       </c>
       <c r="C248">
-        <v>2210.106</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B249">
-        <v>2014</v>
+        <v>1991</v>
       </c>
       <c r="C249">
-        <v>1273.775</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B250">
-        <v>2015</v>
+        <v>1992</v>
       </c>
       <c r="C250">
-        <v>24.05</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B251">
-        <v>2016</v>
+        <v>1993</v>
       </c>
       <c r="C251">
-        <v>186.57</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B252">
-        <v>2017</v>
+        <v>1994</v>
       </c>
       <c r="C252">
-        <v>621.994</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B253">
-        <v>2018</v>
+        <v>1995</v>
       </c>
       <c r="C253">
-        <v>2216.99</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B254">
-        <v>2019</v>
+        <v>1996</v>
       </c>
       <c r="C254">
-        <v>793.841</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B255">
-        <v>2020</v>
+        <v>1997</v>
       </c>
       <c r="C255">
-        <v>411.605</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B256">
-        <v>2021</v>
+        <v>1998</v>
       </c>
       <c r="C256">
-        <v>155.539</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B257">
-        <v>2022</v>
+        <v>1999</v>
       </c>
       <c r="C257">
-        <v>151.855</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B258">
-        <v>2023</v>
+        <v>2000</v>
       </c>
       <c r="C258">
-        <v>214.405</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B259">
-        <v>2024</v>
+        <v>2001</v>
       </c>
       <c r="C259">
-        <v>286.399</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B260">
-        <v>2025</v>
+        <v>2002</v>
       </c>
       <c r="C260">
-        <v>61.892</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -3287,10 +3287,10 @@
         <v>11</v>
       </c>
       <c r="B261">
-        <v>1989</v>
+        <v>2003</v>
       </c>
       <c r="C261">
-        <v>165.696</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -3298,10 +3298,10 @@
         <v>11</v>
       </c>
       <c r="B262">
-        <v>1990</v>
+        <v>2004</v>
       </c>
       <c r="C262">
-        <v>207.517</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -3309,10 +3309,10 @@
         <v>11</v>
       </c>
       <c r="B263">
-        <v>1991</v>
+        <v>2005</v>
       </c>
       <c r="C263">
-        <v>242.225</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -3320,10 +3320,10 @@
         <v>11</v>
       </c>
       <c r="B264">
-        <v>1992</v>
+        <v>2006</v>
       </c>
       <c r="C264">
-        <v>1116.246</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -3331,10 +3331,10 @@
         <v>11</v>
       </c>
       <c r="B265">
-        <v>1993</v>
+        <v>2007</v>
       </c>
       <c r="C265">
-        <v>148.56</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -3342,10 +3342,10 @@
         <v>11</v>
       </c>
       <c r="B266">
-        <v>1994</v>
+        <v>2008</v>
       </c>
       <c r="C266">
-        <v>671.263</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -3353,10 +3353,10 @@
         <v>11</v>
       </c>
       <c r="B267">
-        <v>1995</v>
+        <v>2009</v>
       </c>
       <c r="C267">
-        <v>868.654</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -3364,10 +3364,10 @@
         <v>11</v>
       </c>
       <c r="B268">
-        <v>1996</v>
+        <v>2010</v>
       </c>
       <c r="C268">
-        <v>966.037</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -3375,10 +3375,10 @@
         <v>11</v>
       </c>
       <c r="B269">
-        <v>1997</v>
+        <v>2011</v>
       </c>
       <c r="C269">
-        <v>2194.416</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -3386,10 +3386,10 @@
         <v>11</v>
       </c>
       <c r="B270">
-        <v>1998</v>
+        <v>2012</v>
       </c>
       <c r="C270">
-        <v>1882.119</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -3397,10 +3397,10 @@
         <v>11</v>
       </c>
       <c r="B271">
-        <v>1999</v>
+        <v>2013</v>
       </c>
       <c r="C271">
-        <v>1622.012</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -3408,10 +3408,10 @@
         <v>11</v>
       </c>
       <c r="B272">
-        <v>2000</v>
+        <v>2014</v>
       </c>
       <c r="C272">
-        <v>1075.395</v>
+        <v>151</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -3419,10 +3419,10 @@
         <v>11</v>
       </c>
       <c r="B273">
-        <v>2001</v>
+        <v>2015</v>
       </c>
       <c r="C273">
-        <v>847.7</v>
+        <v>644</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -3430,10 +3430,10 @@
         <v>11</v>
       </c>
       <c r="B274">
-        <v>2002</v>
+        <v>2016</v>
       </c>
       <c r="C274">
-        <v>1751.447</v>
+        <v>650</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -3441,10 +3441,10 @@
         <v>11</v>
       </c>
       <c r="B275">
-        <v>2003</v>
+        <v>2017</v>
       </c>
       <c r="C275">
-        <v>1398.02</v>
+        <v>657</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -3452,10 +3452,10 @@
         <v>11</v>
       </c>
       <c r="B276">
-        <v>2004</v>
+        <v>2018</v>
       </c>
       <c r="C276">
-        <v>1085.991</v>
+        <v>554.5</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -3463,10 +3463,10 @@
         <v>11</v>
       </c>
       <c r="B277">
-        <v>2005</v>
+        <v>2019</v>
       </c>
       <c r="C277">
-        <v>1460.566</v>
+        <v>806</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -3474,10 +3474,10 @@
         <v>11</v>
       </c>
       <c r="B278">
-        <v>2006</v>
+        <v>2020</v>
       </c>
       <c r="C278">
-        <v>1937.453</v>
+        <v>410</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -3485,10 +3485,10 @@
         <v>11</v>
       </c>
       <c r="B279">
-        <v>2007</v>
+        <v>2021</v>
       </c>
       <c r="C279">
-        <v>2292.716</v>
+        <v>160</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -3496,10 +3496,10 @@
         <v>11</v>
       </c>
       <c r="B280">
-        <v>2008</v>
+        <v>2022</v>
       </c>
       <c r="C280">
-        <v>2033.549</v>
+        <v>176</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -3507,186 +3507,186 @@
         <v>11</v>
       </c>
       <c r="B281">
-        <v>2009</v>
+        <v>2023</v>
       </c>
       <c r="C281">
-        <v>1373.338</v>
+        <v>248</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B282">
-        <v>2010</v>
+        <v>1989</v>
       </c>
       <c r="C282">
-        <v>1442.3</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B283">
-        <v>2011</v>
+        <v>1990</v>
       </c>
       <c r="C283">
-        <v>1911.578</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B284">
-        <v>2012</v>
+        <v>1991</v>
       </c>
       <c r="C284">
-        <v>2488.848</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B285">
-        <v>2013</v>
+        <v>1992</v>
       </c>
       <c r="C285">
-        <v>2210.106</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B286">
-        <v>2014</v>
+        <v>1993</v>
       </c>
       <c r="C286">
-        <v>1273.775</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B287">
-        <v>2015</v>
+        <v>1994</v>
       </c>
       <c r="C287">
-        <v>24.05</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B288">
-        <v>2016</v>
+        <v>1995</v>
       </c>
       <c r="C288">
-        <v>186.57</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B289">
-        <v>2017</v>
+        <v>1996</v>
       </c>
       <c r="C289">
-        <v>621.994</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B290">
-        <v>2018</v>
+        <v>1997</v>
       </c>
       <c r="C290">
-        <v>2216.99</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B291">
-        <v>2019</v>
+        <v>1998</v>
       </c>
       <c r="C291">
-        <v>793.841</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B292">
-        <v>2020</v>
+        <v>1999</v>
       </c>
       <c r="C292">
-        <v>411.605</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B293">
-        <v>2021</v>
+        <v>2000</v>
       </c>
       <c r="C293">
-        <v>155.539</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B294">
-        <v>2022</v>
+        <v>2001</v>
       </c>
       <c r="C294">
-        <v>151.855</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B295">
-        <v>2023</v>
+        <v>2002</v>
       </c>
       <c r="C295">
-        <v>214.405</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B296">
-        <v>2024</v>
+        <v>2003</v>
       </c>
       <c r="C296">
-        <v>286.399</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B297">
-        <v>2025</v>
+        <v>2004</v>
       </c>
       <c r="C297">
-        <v>61.892</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -3694,10 +3694,10 @@
         <v>12</v>
       </c>
       <c r="B298">
-        <v>1989</v>
+        <v>2005</v>
       </c>
       <c r="C298">
-        <v>165.696</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -3705,10 +3705,10 @@
         <v>12</v>
       </c>
       <c r="B299">
-        <v>1990</v>
+        <v>2006</v>
       </c>
       <c r="C299">
-        <v>207.517</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -3716,10 +3716,10 @@
         <v>12</v>
       </c>
       <c r="B300">
-        <v>1991</v>
+        <v>2007</v>
       </c>
       <c r="C300">
-        <v>242.225</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -3727,10 +3727,10 @@
         <v>12</v>
       </c>
       <c r="B301">
-        <v>1992</v>
+        <v>2008</v>
       </c>
       <c r="C301">
-        <v>1116.246</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -3738,10 +3738,10 @@
         <v>12</v>
       </c>
       <c r="B302">
-        <v>1993</v>
+        <v>2009</v>
       </c>
       <c r="C302">
-        <v>148.56</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -3749,10 +3749,10 @@
         <v>12</v>
       </c>
       <c r="B303">
-        <v>1994</v>
+        <v>2010</v>
       </c>
       <c r="C303">
-        <v>671.263</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -3760,10 +3760,10 @@
         <v>12</v>
       </c>
       <c r="B304">
-        <v>1995</v>
+        <v>2011</v>
       </c>
       <c r="C304">
-        <v>868.654</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -3771,10 +3771,10 @@
         <v>12</v>
       </c>
       <c r="B305">
-        <v>1996</v>
+        <v>2012</v>
       </c>
       <c r="C305">
-        <v>966.037</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -3782,10 +3782,10 @@
         <v>12</v>
       </c>
       <c r="B306">
-        <v>1997</v>
+        <v>2013</v>
       </c>
       <c r="C306">
-        <v>2194.416</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -3793,10 +3793,10 @@
         <v>12</v>
       </c>
       <c r="B307">
-        <v>1998</v>
+        <v>2014</v>
       </c>
       <c r="C307">
-        <v>1882.119</v>
+        <v>151</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -3804,10 +3804,10 @@
         <v>12</v>
       </c>
       <c r="B308">
-        <v>1999</v>
+        <v>2015</v>
       </c>
       <c r="C308">
-        <v>1622.012</v>
+        <v>644</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -3815,10 +3815,10 @@
         <v>12</v>
       </c>
       <c r="B309">
-        <v>2000</v>
+        <v>2016</v>
       </c>
       <c r="C309">
-        <v>1075.395</v>
+        <v>650</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -3826,10 +3826,10 @@
         <v>12</v>
       </c>
       <c r="B310">
-        <v>2001</v>
+        <v>2017</v>
       </c>
       <c r="C310">
-        <v>847.7</v>
+        <v>657</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -3837,10 +3837,10 @@
         <v>12</v>
       </c>
       <c r="B311">
-        <v>2002</v>
+        <v>2018</v>
       </c>
       <c r="C311">
-        <v>1751.447</v>
+        <v>554.5</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -3848,10 +3848,10 @@
         <v>12</v>
       </c>
       <c r="B312">
-        <v>2003</v>
+        <v>2019</v>
       </c>
       <c r="C312">
-        <v>1398.02</v>
+        <v>806</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -3859,10 +3859,10 @@
         <v>12</v>
       </c>
       <c r="B313">
-        <v>2004</v>
+        <v>2020</v>
       </c>
       <c r="C313">
-        <v>1085.991</v>
+        <v>410</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -3870,10 +3870,10 @@
         <v>12</v>
       </c>
       <c r="B314">
-        <v>2005</v>
+        <v>2021</v>
       </c>
       <c r="C314">
-        <v>1460.566</v>
+        <v>160</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -3881,10 +3881,10 @@
         <v>12</v>
       </c>
       <c r="B315">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="C315">
-        <v>1937.453</v>
+        <v>176</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -3892,208 +3892,208 @@
         <v>12</v>
       </c>
       <c r="B316">
-        <v>2007</v>
+        <v>2023</v>
       </c>
       <c r="C316">
-        <v>2292.716</v>
+        <v>248</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B317">
-        <v>2008</v>
+        <v>1989</v>
       </c>
       <c r="C317">
-        <v>2033.549</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B318">
-        <v>2009</v>
+        <v>1990</v>
       </c>
       <c r="C318">
-        <v>1373.338</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B319">
-        <v>2010</v>
+        <v>1991</v>
       </c>
       <c r="C319">
-        <v>1442.3</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B320">
-        <v>2011</v>
+        <v>1992</v>
       </c>
       <c r="C320">
-        <v>1911.578</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B321">
-        <v>2012</v>
+        <v>1993</v>
       </c>
       <c r="C321">
-        <v>2488.848</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B322">
-        <v>2013</v>
+        <v>1994</v>
       </c>
       <c r="C322">
-        <v>2210.106</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B323">
-        <v>2014</v>
+        <v>1995</v>
       </c>
       <c r="C323">
-        <v>1273.775</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B324">
-        <v>2015</v>
+        <v>1996</v>
       </c>
       <c r="C324">
-        <v>24.05</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B325">
-        <v>2016</v>
+        <v>1997</v>
       </c>
       <c r="C325">
-        <v>186.57</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B326">
-        <v>2017</v>
+        <v>1998</v>
       </c>
       <c r="C326">
-        <v>621.994</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B327">
-        <v>2018</v>
+        <v>1999</v>
       </c>
       <c r="C327">
-        <v>2216.99</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B328">
-        <v>2019</v>
+        <v>2000</v>
       </c>
       <c r="C328">
-        <v>793.841</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B329">
-        <v>2020</v>
+        <v>2001</v>
       </c>
       <c r="C329">
-        <v>411.605</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B330">
-        <v>2021</v>
+        <v>2002</v>
       </c>
       <c r="C330">
-        <v>155.539</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B331">
-        <v>2022</v>
+        <v>2003</v>
       </c>
       <c r="C331">
-        <v>151.855</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B332">
-        <v>2023</v>
+        <v>2004</v>
       </c>
       <c r="C332">
-        <v>214.405</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B333">
-        <v>2024</v>
+        <v>2005</v>
       </c>
       <c r="C333">
-        <v>286.399</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B334">
-        <v>2025</v>
+        <v>2006</v>
       </c>
       <c r="C334">
-        <v>61.892</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -4101,10 +4101,10 @@
         <v>13</v>
       </c>
       <c r="B335">
-        <v>1989</v>
+        <v>2007</v>
       </c>
       <c r="C335">
-        <v>165.696</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -4112,10 +4112,10 @@
         <v>13</v>
       </c>
       <c r="B336">
-        <v>1990</v>
+        <v>2008</v>
       </c>
       <c r="C336">
-        <v>207.517</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -4123,10 +4123,10 @@
         <v>13</v>
       </c>
       <c r="B337">
-        <v>1991</v>
+        <v>2009</v>
       </c>
       <c r="C337">
-        <v>242.225</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -4134,10 +4134,10 @@
         <v>13</v>
       </c>
       <c r="B338">
-        <v>1992</v>
+        <v>2010</v>
       </c>
       <c r="C338">
-        <v>1116.246</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -4145,10 +4145,10 @@
         <v>13</v>
       </c>
       <c r="B339">
-        <v>1993</v>
+        <v>2011</v>
       </c>
       <c r="C339">
-        <v>148.56</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -4156,10 +4156,10 @@
         <v>13</v>
       </c>
       <c r="B340">
-        <v>1994</v>
+        <v>2012</v>
       </c>
       <c r="C340">
-        <v>671.263</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -4167,10 +4167,10 @@
         <v>13</v>
       </c>
       <c r="B341">
-        <v>1995</v>
+        <v>2013</v>
       </c>
       <c r="C341">
-        <v>868.654</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -4178,10 +4178,10 @@
         <v>13</v>
       </c>
       <c r="B342">
-        <v>1996</v>
+        <v>2014</v>
       </c>
       <c r="C342">
-        <v>966.037</v>
+        <v>151</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -4189,10 +4189,10 @@
         <v>13</v>
       </c>
       <c r="B343">
-        <v>1997</v>
+        <v>2015</v>
       </c>
       <c r="C343">
-        <v>2194.416</v>
+        <v>644</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -4200,10 +4200,10 @@
         <v>13</v>
       </c>
       <c r="B344">
-        <v>1998</v>
+        <v>2016</v>
       </c>
       <c r="C344">
-        <v>1882.119</v>
+        <v>650</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -4211,10 +4211,10 @@
         <v>13</v>
       </c>
       <c r="B345">
-        <v>1999</v>
+        <v>2017</v>
       </c>
       <c r="C345">
-        <v>1622.012</v>
+        <v>657</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -4222,10 +4222,10 @@
         <v>13</v>
       </c>
       <c r="B346">
-        <v>2000</v>
+        <v>2018</v>
       </c>
       <c r="C346">
-        <v>1075.395</v>
+        <v>554.5</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -4233,10 +4233,10 @@
         <v>13</v>
       </c>
       <c r="B347">
-        <v>2001</v>
+        <v>2019</v>
       </c>
       <c r="C347">
-        <v>847.7</v>
+        <v>806</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -4244,10 +4244,10 @@
         <v>13</v>
       </c>
       <c r="B348">
-        <v>2002</v>
+        <v>2020</v>
       </c>
       <c r="C348">
-        <v>1751.447</v>
+        <v>410</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -4255,10 +4255,10 @@
         <v>13</v>
       </c>
       <c r="B349">
-        <v>2003</v>
+        <v>2021</v>
       </c>
       <c r="C349">
-        <v>1398.02</v>
+        <v>160</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -4266,10 +4266,10 @@
         <v>13</v>
       </c>
       <c r="B350">
-        <v>2004</v>
+        <v>2022</v>
       </c>
       <c r="C350">
-        <v>1085.991</v>
+        <v>176</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -4277,230 +4277,230 @@
         <v>13</v>
       </c>
       <c r="B351">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="C351">
-        <v>1460.566</v>
+        <v>248</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B352">
-        <v>2006</v>
+        <v>1989</v>
       </c>
       <c r="C352">
-        <v>1937.453</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B353">
-        <v>2007</v>
+        <v>1990</v>
       </c>
       <c r="C353">
-        <v>2292.716</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B354">
-        <v>2008</v>
+        <v>1991</v>
       </c>
       <c r="C354">
-        <v>2033.549</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="355" spans="1:3">
       <c r="A355" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B355">
-        <v>2009</v>
+        <v>1992</v>
       </c>
       <c r="C355">
-        <v>1373.338</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B356">
-        <v>2010</v>
+        <v>1993</v>
       </c>
       <c r="C356">
-        <v>1442.3</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B357">
-        <v>2011</v>
+        <v>1994</v>
       </c>
       <c r="C357">
-        <v>1911.578</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B358">
-        <v>2012</v>
+        <v>1995</v>
       </c>
       <c r="C358">
-        <v>2488.848</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B359">
-        <v>2013</v>
+        <v>1996</v>
       </c>
       <c r="C359">
-        <v>2210.106</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B360">
-        <v>2014</v>
+        <v>1997</v>
       </c>
       <c r="C360">
-        <v>1273.775</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B361">
-        <v>2015</v>
+        <v>1998</v>
       </c>
       <c r="C361">
-        <v>24.05</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B362">
-        <v>2016</v>
+        <v>1999</v>
       </c>
       <c r="C362">
-        <v>186.57</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B363">
-        <v>2017</v>
+        <v>2000</v>
       </c>
       <c r="C363">
-        <v>621.994</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B364">
-        <v>2018</v>
+        <v>2001</v>
       </c>
       <c r="C364">
-        <v>2216.99</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B365">
-        <v>2019</v>
+        <v>2002</v>
       </c>
       <c r="C365">
-        <v>793.841</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B366">
-        <v>2020</v>
+        <v>2003</v>
       </c>
       <c r="C366">
-        <v>411.605</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B367">
-        <v>2021</v>
+        <v>2004</v>
       </c>
       <c r="C367">
-        <v>155.539</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B368">
-        <v>2022</v>
+        <v>2005</v>
       </c>
       <c r="C368">
-        <v>151.855</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B369">
-        <v>2023</v>
+        <v>2006</v>
       </c>
       <c r="C369">
-        <v>214.405</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B370">
-        <v>2024</v>
+        <v>2007</v>
       </c>
       <c r="C370">
-        <v>286.399</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B371">
-        <v>2025</v>
+        <v>2008</v>
       </c>
       <c r="C371">
-        <v>61.892</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -4508,10 +4508,10 @@
         <v>14</v>
       </c>
       <c r="B372">
-        <v>1989</v>
+        <v>2009</v>
       </c>
       <c r="C372">
-        <v>165.696</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -4519,10 +4519,10 @@
         <v>14</v>
       </c>
       <c r="B373">
-        <v>1990</v>
+        <v>2010</v>
       </c>
       <c r="C373">
-        <v>207.517</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -4530,10 +4530,10 @@
         <v>14</v>
       </c>
       <c r="B374">
-        <v>1991</v>
+        <v>2011</v>
       </c>
       <c r="C374">
-        <v>242.225</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -4541,10 +4541,10 @@
         <v>14</v>
       </c>
       <c r="B375">
-        <v>1992</v>
+        <v>2012</v>
       </c>
       <c r="C375">
-        <v>1116.246</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -4552,10 +4552,10 @@
         <v>14</v>
       </c>
       <c r="B376">
-        <v>1993</v>
+        <v>2013</v>
       </c>
       <c r="C376">
-        <v>148.56</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -4563,10 +4563,10 @@
         <v>14</v>
       </c>
       <c r="B377">
-        <v>1994</v>
+        <v>2014</v>
       </c>
       <c r="C377">
-        <v>671.263</v>
+        <v>151</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -4574,10 +4574,10 @@
         <v>14</v>
       </c>
       <c r="B378">
-        <v>1995</v>
+        <v>2015</v>
       </c>
       <c r="C378">
-        <v>868.654</v>
+        <v>644</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -4585,10 +4585,10 @@
         <v>14</v>
       </c>
       <c r="B379">
-        <v>1996</v>
+        <v>2016</v>
       </c>
       <c r="C379">
-        <v>966.037</v>
+        <v>650</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -4596,10 +4596,10 @@
         <v>14</v>
       </c>
       <c r="B380">
-        <v>1997</v>
+        <v>2017</v>
       </c>
       <c r="C380">
-        <v>2194.416</v>
+        <v>657</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -4607,10 +4607,10 @@
         <v>14</v>
       </c>
       <c r="B381">
-        <v>1998</v>
+        <v>2018</v>
       </c>
       <c r="C381">
-        <v>1882.119</v>
+        <v>554.5</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -4618,10 +4618,10 @@
         <v>14</v>
       </c>
       <c r="B382">
-        <v>1999</v>
+        <v>2019</v>
       </c>
       <c r="C382">
-        <v>1622.012</v>
+        <v>806</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -4629,10 +4629,10 @@
         <v>14</v>
       </c>
       <c r="B383">
-        <v>2000</v>
+        <v>2020</v>
       </c>
       <c r="C383">
-        <v>1075.395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -4640,10 +4640,10 @@
         <v>14</v>
       </c>
       <c r="B384">
-        <v>2001</v>
+        <v>2021</v>
       </c>
       <c r="C384">
-        <v>847.7</v>
+        <v>160</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -4651,10 +4651,10 @@
         <v>14</v>
       </c>
       <c r="B385">
-        <v>2002</v>
+        <v>2022</v>
       </c>
       <c r="C385">
-        <v>1751.447</v>
+        <v>176</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -4662,252 +4662,252 @@
         <v>14</v>
       </c>
       <c r="B386">
-        <v>2003</v>
+        <v>2023</v>
       </c>
       <c r="C386">
-        <v>1398.02</v>
+        <v>248</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B387">
-        <v>2004</v>
+        <v>1989</v>
       </c>
       <c r="C387">
-        <v>1085.991</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="388" spans="1:3">
       <c r="A388" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B388">
-        <v>2005</v>
+        <v>1990</v>
       </c>
       <c r="C388">
-        <v>1460.566</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B389">
-        <v>2006</v>
+        <v>1991</v>
       </c>
       <c r="C389">
-        <v>1937.453</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="390" spans="1:3">
       <c r="A390" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B390">
-        <v>2007</v>
+        <v>1992</v>
       </c>
       <c r="C390">
-        <v>2292.716</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B391">
-        <v>2008</v>
+        <v>1993</v>
       </c>
       <c r="C391">
-        <v>2033.549</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B392">
-        <v>2009</v>
+        <v>1994</v>
       </c>
       <c r="C392">
-        <v>1373.338</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B393">
-        <v>2010</v>
+        <v>1995</v>
       </c>
       <c r="C393">
-        <v>1442.3</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B394">
-        <v>2011</v>
+        <v>1996</v>
       </c>
       <c r="C394">
-        <v>1911.578</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B395">
-        <v>2012</v>
+        <v>1997</v>
       </c>
       <c r="C395">
-        <v>2488.848</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B396">
-        <v>2013</v>
+        <v>1998</v>
       </c>
       <c r="C396">
-        <v>2210.106</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B397">
-        <v>2014</v>
+        <v>1999</v>
       </c>
       <c r="C397">
-        <v>1273.775</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B398">
-        <v>2015</v>
+        <v>2000</v>
       </c>
       <c r="C398">
-        <v>24.05</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B399">
-        <v>2016</v>
+        <v>2001</v>
       </c>
       <c r="C399">
-        <v>186.57</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="400" spans="1:3">
       <c r="A400" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B400">
-        <v>2017</v>
+        <v>2002</v>
       </c>
       <c r="C400">
-        <v>621.994</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="401" spans="1:3">
       <c r="A401" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B401">
-        <v>2018</v>
+        <v>2003</v>
       </c>
       <c r="C401">
-        <v>2216.99</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B402">
-        <v>2019</v>
+        <v>2004</v>
       </c>
       <c r="C402">
-        <v>793.841</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B403">
-        <v>2020</v>
+        <v>2005</v>
       </c>
       <c r="C403">
-        <v>411.605</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B404">
-        <v>2021</v>
+        <v>2006</v>
       </c>
       <c r="C404">
-        <v>155.539</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B405">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="C405">
-        <v>151.855</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B406">
-        <v>2023</v>
+        <v>2008</v>
       </c>
       <c r="C406">
-        <v>214.405</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="407" spans="1:3">
       <c r="A407" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B407">
-        <v>2024</v>
+        <v>2009</v>
       </c>
       <c r="C407">
-        <v>286.399</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="408" spans="1:3">
       <c r="A408" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B408">
-        <v>2025</v>
+        <v>2010</v>
       </c>
       <c r="C408">
-        <v>61.892</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="409" spans="1:3">
@@ -4915,10 +4915,10 @@
         <v>15</v>
       </c>
       <c r="B409">
-        <v>1989</v>
+        <v>2011</v>
       </c>
       <c r="C409">
-        <v>165.696</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -4926,10 +4926,10 @@
         <v>15</v>
       </c>
       <c r="B410">
-        <v>1990</v>
+        <v>2012</v>
       </c>
       <c r="C410">
-        <v>207.517</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -4937,10 +4937,10 @@
         <v>15</v>
       </c>
       <c r="B411">
-        <v>1991</v>
+        <v>2013</v>
       </c>
       <c r="C411">
-        <v>242.225</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -4948,10 +4948,10 @@
         <v>15</v>
       </c>
       <c r="B412">
-        <v>1992</v>
+        <v>2014</v>
       </c>
       <c r="C412">
-        <v>1116.246</v>
+        <v>151</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -4959,10 +4959,10 @@
         <v>15</v>
       </c>
       <c r="B413">
-        <v>1993</v>
+        <v>2015</v>
       </c>
       <c r="C413">
-        <v>148.56</v>
+        <v>644</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -4970,10 +4970,10 @@
         <v>15</v>
       </c>
       <c r="B414">
-        <v>1994</v>
+        <v>2016</v>
       </c>
       <c r="C414">
-        <v>671.263</v>
+        <v>650</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -4981,10 +4981,10 @@
         <v>15</v>
       </c>
       <c r="B415">
-        <v>1995</v>
+        <v>2017</v>
       </c>
       <c r="C415">
-        <v>868.654</v>
+        <v>657</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -4992,10 +4992,10 @@
         <v>15</v>
       </c>
       <c r="B416">
-        <v>1996</v>
+        <v>2018</v>
       </c>
       <c r="C416">
-        <v>966.037</v>
+        <v>554.5</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -5003,10 +5003,10 @@
         <v>15</v>
       </c>
       <c r="B417">
-        <v>1997</v>
+        <v>2019</v>
       </c>
       <c r="C417">
-        <v>2194.416</v>
+        <v>806</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -5014,10 +5014,10 @@
         <v>15</v>
       </c>
       <c r="B418">
-        <v>1998</v>
+        <v>2020</v>
       </c>
       <c r="C418">
-        <v>1882.119</v>
+        <v>410</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -5025,10 +5025,10 @@
         <v>15</v>
       </c>
       <c r="B419">
-        <v>1999</v>
+        <v>2021</v>
       </c>
       <c r="C419">
-        <v>1622.012</v>
+        <v>160</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -5036,10 +5036,10 @@
         <v>15</v>
       </c>
       <c r="B420">
-        <v>2000</v>
+        <v>2022</v>
       </c>
       <c r="C420">
-        <v>1075.395</v>
+        <v>176</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -5047,274 +5047,274 @@
         <v>15</v>
       </c>
       <c r="B421">
-        <v>2001</v>
+        <v>2023</v>
       </c>
       <c r="C421">
-        <v>847.7</v>
+        <v>248</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B422">
-        <v>2002</v>
+        <v>1989</v>
       </c>
       <c r="C422">
-        <v>1751.447</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B423">
-        <v>2003</v>
+        <v>1990</v>
       </c>
       <c r="C423">
-        <v>1398.02</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B424">
-        <v>2004</v>
+        <v>1991</v>
       </c>
       <c r="C424">
-        <v>1085.991</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B425">
-        <v>2005</v>
+        <v>1992</v>
       </c>
       <c r="C425">
-        <v>1460.566</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B426">
-        <v>2006</v>
+        <v>1993</v>
       </c>
       <c r="C426">
-        <v>1937.453</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B427">
-        <v>2007</v>
+        <v>1994</v>
       </c>
       <c r="C427">
-        <v>2292.716</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B428">
-        <v>2008</v>
+        <v>1995</v>
       </c>
       <c r="C428">
-        <v>2033.549</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B429">
-        <v>2009</v>
+        <v>1996</v>
       </c>
       <c r="C429">
-        <v>1373.338</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B430">
-        <v>2010</v>
+        <v>1997</v>
       </c>
       <c r="C430">
-        <v>1442.3</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B431">
-        <v>2011</v>
+        <v>1998</v>
       </c>
       <c r="C431">
-        <v>1911.578</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B432">
-        <v>2012</v>
+        <v>1999</v>
       </c>
       <c r="C432">
-        <v>2488.848</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B433">
-        <v>2013</v>
+        <v>2000</v>
       </c>
       <c r="C433">
-        <v>2210.106</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B434">
-        <v>2014</v>
+        <v>2001</v>
       </c>
       <c r="C434">
-        <v>1273.775</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B435">
-        <v>2015</v>
+        <v>2002</v>
       </c>
       <c r="C435">
-        <v>24.05</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="436" spans="1:3">
       <c r="A436" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B436">
-        <v>2016</v>
+        <v>2003</v>
       </c>
       <c r="C436">
-        <v>186.57</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="437" spans="1:3">
       <c r="A437" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B437">
-        <v>2017</v>
+        <v>2004</v>
       </c>
       <c r="C437">
-        <v>621.994</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="438" spans="1:3">
       <c r="A438" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B438">
-        <v>2018</v>
+        <v>2005</v>
       </c>
       <c r="C438">
-        <v>2216.99</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="439" spans="1:3">
       <c r="A439" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B439">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="C439">
-        <v>793.841</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B440">
-        <v>2020</v>
+        <v>2007</v>
       </c>
       <c r="C440">
-        <v>411.605</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B441">
-        <v>2021</v>
+        <v>2008</v>
       </c>
       <c r="C441">
-        <v>155.539</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B442">
-        <v>2022</v>
+        <v>2009</v>
       </c>
       <c r="C442">
-        <v>151.855</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="443" spans="1:3">
       <c r="A443" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B443">
-        <v>2023</v>
+        <v>2010</v>
       </c>
       <c r="C443">
-        <v>214.405</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B444">
-        <v>2024</v>
+        <v>2011</v>
       </c>
       <c r="C444">
-        <v>286.399</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B445">
-        <v>2025</v>
+        <v>2012</v>
       </c>
       <c r="C445">
-        <v>61.892</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -5322,10 +5322,10 @@
         <v>16</v>
       </c>
       <c r="B446">
-        <v>1989</v>
+        <v>2013</v>
       </c>
       <c r="C446">
-        <v>165.696</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -5333,10 +5333,10 @@
         <v>16</v>
       </c>
       <c r="B447">
-        <v>1990</v>
+        <v>2014</v>
       </c>
       <c r="C447">
-        <v>207.517</v>
+        <v>151</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -5344,10 +5344,10 @@
         <v>16</v>
       </c>
       <c r="B448">
-        <v>1991</v>
+        <v>2015</v>
       </c>
       <c r="C448">
-        <v>242.225</v>
+        <v>644</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -5355,10 +5355,10 @@
         <v>16</v>
       </c>
       <c r="B449">
-        <v>1992</v>
+        <v>2016</v>
       </c>
       <c r="C449">
-        <v>1116.246</v>
+        <v>650</v>
       </c>
     </row>
     <row r="450" spans="1:3">
@@ -5366,10 +5366,10 @@
         <v>16</v>
       </c>
       <c r="B450">
-        <v>1993</v>
+        <v>2017</v>
       </c>
       <c r="C450">
-        <v>148.56</v>
+        <v>657</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -5377,10 +5377,10 @@
         <v>16</v>
       </c>
       <c r="B451">
-        <v>1994</v>
+        <v>2018</v>
       </c>
       <c r="C451">
-        <v>671.263</v>
+        <v>554.5</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -5388,10 +5388,10 @@
         <v>16</v>
       </c>
       <c r="B452">
-        <v>1995</v>
+        <v>2019</v>
       </c>
       <c r="C452">
-        <v>868.654</v>
+        <v>806</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -5399,10 +5399,10 @@
         <v>16</v>
       </c>
       <c r="B453">
-        <v>1996</v>
+        <v>2020</v>
       </c>
       <c r="C453">
-        <v>966.037</v>
+        <v>410</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -5410,10 +5410,10 @@
         <v>16</v>
       </c>
       <c r="B454">
-        <v>1997</v>
+        <v>2021</v>
       </c>
       <c r="C454">
-        <v>2194.416</v>
+        <v>160</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -5421,10 +5421,10 @@
         <v>16</v>
       </c>
       <c r="B455">
-        <v>1998</v>
+        <v>2022</v>
       </c>
       <c r="C455">
-        <v>1882.119</v>
+        <v>176</v>
       </c>
     </row>
     <row r="456" spans="1:3">
@@ -5432,296 +5432,296 @@
         <v>16</v>
       </c>
       <c r="B456">
-        <v>1999</v>
+        <v>2023</v>
       </c>
       <c r="C456">
-        <v>1622.012</v>
+        <v>248</v>
       </c>
     </row>
     <row r="457" spans="1:3">
       <c r="A457" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B457">
-        <v>2000</v>
+        <v>1989</v>
       </c>
       <c r="C457">
-        <v>1075.395</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B458">
-        <v>2001</v>
+        <v>1990</v>
       </c>
       <c r="C458">
-        <v>847.7</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="A459" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B459">
-        <v>2002</v>
+        <v>1991</v>
       </c>
       <c r="C459">
-        <v>1751.447</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B460">
-        <v>2003</v>
+        <v>1992</v>
       </c>
       <c r="C460">
-        <v>1398.02</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B461">
-        <v>2004</v>
+        <v>1993</v>
       </c>
       <c r="C461">
-        <v>1085.991</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B462">
-        <v>2005</v>
+        <v>1994</v>
       </c>
       <c r="C462">
-        <v>1460.566</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B463">
-        <v>2006</v>
+        <v>1995</v>
       </c>
       <c r="C463">
-        <v>1937.453</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B464">
-        <v>2007</v>
+        <v>1996</v>
       </c>
       <c r="C464">
-        <v>2292.716</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B465">
-        <v>2008</v>
+        <v>1997</v>
       </c>
       <c r="C465">
-        <v>2033.549</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B466">
-        <v>2009</v>
+        <v>1998</v>
       </c>
       <c r="C466">
-        <v>1373.338</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B467">
-        <v>2010</v>
+        <v>1999</v>
       </c>
       <c r="C467">
-        <v>1442.3</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B468">
-        <v>2011</v>
+        <v>2000</v>
       </c>
       <c r="C468">
-        <v>1911.578</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="469" spans="1:3">
       <c r="A469" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B469">
-        <v>2012</v>
+        <v>2001</v>
       </c>
       <c r="C469">
-        <v>2488.848</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B470">
-        <v>2013</v>
+        <v>2002</v>
       </c>
       <c r="C470">
-        <v>2210.106</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B471">
-        <v>2014</v>
+        <v>2003</v>
       </c>
       <c r="C471">
-        <v>1273.775</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="472" spans="1:3">
       <c r="A472" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B472">
-        <v>2015</v>
+        <v>2004</v>
       </c>
       <c r="C472">
-        <v>24.05</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="473" spans="1:3">
       <c r="A473" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B473">
-        <v>2016</v>
+        <v>2005</v>
       </c>
       <c r="C473">
-        <v>186.57</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="474" spans="1:3">
       <c r="A474" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B474">
-        <v>2017</v>
+        <v>2006</v>
       </c>
       <c r="C474">
-        <v>621.994</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="475" spans="1:3">
       <c r="A475" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B475">
-        <v>2018</v>
+        <v>2007</v>
       </c>
       <c r="C475">
-        <v>2216.99</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B476">
-        <v>2019</v>
+        <v>2008</v>
       </c>
       <c r="C476">
-        <v>793.841</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="477" spans="1:3">
       <c r="A477" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B477">
-        <v>2020</v>
+        <v>2009</v>
       </c>
       <c r="C477">
-        <v>411.605</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="478" spans="1:3">
       <c r="A478" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B478">
-        <v>2021</v>
+        <v>2010</v>
       </c>
       <c r="C478">
-        <v>155.539</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="479" spans="1:3">
       <c r="A479" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B479">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="C479">
-        <v>151.855</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="480" spans="1:3">
       <c r="A480" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B480">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="C480">
-        <v>214.405</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="481" spans="1:3">
       <c r="A481" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B481">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="C481">
-        <v>286.399</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="482" spans="1:3">
       <c r="A482" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B482">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="C482">
-        <v>61.892</v>
+        <v>151</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -5729,10 +5729,10 @@
         <v>17</v>
       </c>
       <c r="B483">
-        <v>1989</v>
+        <v>2015</v>
       </c>
       <c r="C483">
-        <v>165.696</v>
+        <v>644</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -5740,10 +5740,10 @@
         <v>17</v>
       </c>
       <c r="B484">
-        <v>1990</v>
+        <v>2016</v>
       </c>
       <c r="C484">
-        <v>207.517</v>
+        <v>650</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -5751,10 +5751,10 @@
         <v>17</v>
       </c>
       <c r="B485">
-        <v>1991</v>
+        <v>2017</v>
       </c>
       <c r="C485">
-        <v>242.225</v>
+        <v>657</v>
       </c>
     </row>
     <row r="486" spans="1:3">
@@ -5762,10 +5762,10 @@
         <v>17</v>
       </c>
       <c r="B486">
-        <v>1992</v>
+        <v>2018</v>
       </c>
       <c r="C486">
-        <v>1116.246</v>
+        <v>554.5</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -5773,10 +5773,10 @@
         <v>17</v>
       </c>
       <c r="B487">
-        <v>1993</v>
+        <v>2019</v>
       </c>
       <c r="C487">
-        <v>148.56</v>
+        <v>806</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -5784,10 +5784,10 @@
         <v>17</v>
       </c>
       <c r="B488">
-        <v>1994</v>
+        <v>2020</v>
       </c>
       <c r="C488">
-        <v>671.263</v>
+        <v>410</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -5795,10 +5795,10 @@
         <v>17</v>
       </c>
       <c r="B489">
-        <v>1995</v>
+        <v>2021</v>
       </c>
       <c r="C489">
-        <v>868.654</v>
+        <v>160</v>
       </c>
     </row>
     <row r="490" spans="1:3">
@@ -5806,10 +5806,10 @@
         <v>17</v>
       </c>
       <c r="B490">
-        <v>1996</v>
+        <v>2022</v>
       </c>
       <c r="C490">
-        <v>966.037</v>
+        <v>176</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -5817,318 +5817,318 @@
         <v>17</v>
       </c>
       <c r="B491">
-        <v>1997</v>
+        <v>2023</v>
       </c>
       <c r="C491">
-        <v>2194.416</v>
+        <v>248</v>
       </c>
     </row>
     <row r="492" spans="1:3">
       <c r="A492" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B492">
-        <v>1998</v>
+        <v>1989</v>
       </c>
       <c r="C492">
-        <v>1882.119</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="493" spans="1:3">
       <c r="A493" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B493">
-        <v>1999</v>
+        <v>1990</v>
       </c>
       <c r="C493">
-        <v>1622.012</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="494" spans="1:3">
       <c r="A494" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B494">
-        <v>2000</v>
+        <v>1991</v>
       </c>
       <c r="C494">
-        <v>1075.395</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="495" spans="1:3">
       <c r="A495" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B495">
-        <v>2001</v>
+        <v>1992</v>
       </c>
       <c r="C495">
-        <v>847.7</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="496" spans="1:3">
       <c r="A496" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B496">
-        <v>2002</v>
+        <v>1993</v>
       </c>
       <c r="C496">
-        <v>1751.447</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B497">
-        <v>2003</v>
+        <v>1994</v>
       </c>
       <c r="C497">
-        <v>1398.02</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="498" spans="1:3">
       <c r="A498" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B498">
-        <v>2004</v>
+        <v>1995</v>
       </c>
       <c r="C498">
-        <v>1085.991</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="499" spans="1:3">
       <c r="A499" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B499">
-        <v>2005</v>
+        <v>1996</v>
       </c>
       <c r="C499">
-        <v>1460.566</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="500" spans="1:3">
       <c r="A500" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B500">
-        <v>2006</v>
+        <v>1997</v>
       </c>
       <c r="C500">
-        <v>1937.453</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B501">
-        <v>2007</v>
+        <v>1998</v>
       </c>
       <c r="C501">
-        <v>2292.716</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="502" spans="1:3">
       <c r="A502" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B502">
-        <v>2008</v>
+        <v>1999</v>
       </c>
       <c r="C502">
-        <v>2033.549</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="503" spans="1:3">
       <c r="A503" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B503">
-        <v>2009</v>
+        <v>2000</v>
       </c>
       <c r="C503">
-        <v>1373.338</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="504" spans="1:3">
       <c r="A504" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B504">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="C504">
-        <v>1442.3</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="505" spans="1:3">
       <c r="A505" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B505">
-        <v>2011</v>
+        <v>2002</v>
       </c>
       <c r="C505">
-        <v>1911.578</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="506" spans="1:3">
       <c r="A506" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B506">
-        <v>2012</v>
+        <v>2003</v>
       </c>
       <c r="C506">
-        <v>2488.848</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="507" spans="1:3">
       <c r="A507" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B507">
-        <v>2013</v>
+        <v>2004</v>
       </c>
       <c r="C507">
-        <v>2210.106</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="508" spans="1:3">
       <c r="A508" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B508">
-        <v>2014</v>
+        <v>2005</v>
       </c>
       <c r="C508">
-        <v>1273.775</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B509">
-        <v>2015</v>
+        <v>2006</v>
       </c>
       <c r="C509">
-        <v>24.05</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="510" spans="1:3">
       <c r="A510" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B510">
-        <v>2016</v>
+        <v>2007</v>
       </c>
       <c r="C510">
-        <v>186.57</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="511" spans="1:3">
       <c r="A511" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B511">
-        <v>2017</v>
+        <v>2008</v>
       </c>
       <c r="C511">
-        <v>621.994</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="512" spans="1:3">
       <c r="A512" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B512">
-        <v>2018</v>
+        <v>2009</v>
       </c>
       <c r="C512">
-        <v>2216.99</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="513" spans="1:3">
       <c r="A513" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B513">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="C513">
-        <v>793.841</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="514" spans="1:3">
       <c r="A514" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B514">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="C514">
-        <v>411.605</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="515" spans="1:3">
       <c r="A515" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B515">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="C515">
-        <v>155.539</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="516" spans="1:3">
       <c r="A516" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B516">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="C516">
-        <v>151.855</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B517">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="C517">
-        <v>214.405</v>
+        <v>151</v>
       </c>
     </row>
     <row r="518" spans="1:3">
       <c r="A518" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B518">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="C518">
-        <v>286.399</v>
+        <v>644</v>
       </c>
     </row>
     <row r="519" spans="1:3">
       <c r="A519" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B519">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="C519">
-        <v>61.892</v>
+        <v>650</v>
       </c>
     </row>
     <row r="520" spans="1:3">
@@ -6136,10 +6136,10 @@
         <v>18</v>
       </c>
       <c r="B520">
-        <v>1989</v>
+        <v>2017</v>
       </c>
       <c r="C520">
-        <v>165.696</v>
+        <v>657</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -6147,10 +6147,10 @@
         <v>18</v>
       </c>
       <c r="B521">
-        <v>1990</v>
+        <v>2018</v>
       </c>
       <c r="C521">
-        <v>207.517</v>
+        <v>554.5</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -6158,10 +6158,10 @@
         <v>18</v>
       </c>
       <c r="B522">
-        <v>1991</v>
+        <v>2019</v>
       </c>
       <c r="C522">
-        <v>242.225</v>
+        <v>806</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -6169,10 +6169,10 @@
         <v>18</v>
       </c>
       <c r="B523">
-        <v>1992</v>
+        <v>2020</v>
       </c>
       <c r="C523">
-        <v>1116.246</v>
+        <v>410</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -6180,10 +6180,10 @@
         <v>18</v>
       </c>
       <c r="B524">
-        <v>1993</v>
+        <v>2021</v>
       </c>
       <c r="C524">
-        <v>148.56</v>
+        <v>160</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -6191,10 +6191,10 @@
         <v>18</v>
       </c>
       <c r="B525">
-        <v>1994</v>
+        <v>2022</v>
       </c>
       <c r="C525">
-        <v>671.263</v>
+        <v>176</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -6202,340 +6202,340 @@
         <v>18</v>
       </c>
       <c r="B526">
-        <v>1995</v>
+        <v>2023</v>
       </c>
       <c r="C526">
-        <v>868.654</v>
+        <v>248</v>
       </c>
     </row>
     <row r="527" spans="1:3">
       <c r="A527" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B527">
-        <v>1996</v>
+        <v>1989</v>
       </c>
       <c r="C527">
-        <v>966.037</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="528" spans="1:3">
       <c r="A528" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B528">
-        <v>1997</v>
+        <v>1990</v>
       </c>
       <c r="C528">
-        <v>2194.416</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="529" spans="1:3">
       <c r="A529" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B529">
-        <v>1998</v>
+        <v>1991</v>
       </c>
       <c r="C529">
-        <v>1882.119</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="530" spans="1:3">
       <c r="A530" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B530">
-        <v>1999</v>
+        <v>1992</v>
       </c>
       <c r="C530">
-        <v>1622.012</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="531" spans="1:3">
       <c r="A531" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B531">
-        <v>2000</v>
+        <v>1993</v>
       </c>
       <c r="C531">
-        <v>1075.395</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="532" spans="1:3">
       <c r="A532" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B532">
-        <v>2001</v>
+        <v>1994</v>
       </c>
       <c r="C532">
-        <v>847.7</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="533" spans="1:3">
       <c r="A533" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B533">
-        <v>2002</v>
+        <v>1995</v>
       </c>
       <c r="C533">
-        <v>1751.447</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="534" spans="1:3">
       <c r="A534" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B534">
-        <v>2003</v>
+        <v>1996</v>
       </c>
       <c r="C534">
-        <v>1398.02</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="535" spans="1:3">
       <c r="A535" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B535">
-        <v>2004</v>
+        <v>1997</v>
       </c>
       <c r="C535">
-        <v>1085.991</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="536" spans="1:3">
       <c r="A536" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B536">
-        <v>2005</v>
+        <v>1998</v>
       </c>
       <c r="C536">
-        <v>1460.566</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="537" spans="1:3">
       <c r="A537" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B537">
-        <v>2006</v>
+        <v>1999</v>
       </c>
       <c r="C537">
-        <v>1937.453</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="538" spans="1:3">
       <c r="A538" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B538">
-        <v>2007</v>
+        <v>2000</v>
       </c>
       <c r="C538">
-        <v>2292.716</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="539" spans="1:3">
       <c r="A539" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B539">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="C539">
-        <v>2033.549</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="540" spans="1:3">
       <c r="A540" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B540">
-        <v>2009</v>
+        <v>2002</v>
       </c>
       <c r="C540">
-        <v>1373.338</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="541" spans="1:3">
       <c r="A541" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B541">
-        <v>2010</v>
+        <v>2003</v>
       </c>
       <c r="C541">
-        <v>1442.3</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="542" spans="1:3">
       <c r="A542" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B542">
-        <v>2011</v>
+        <v>2004</v>
       </c>
       <c r="C542">
-        <v>1911.578</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="543" spans="1:3">
       <c r="A543" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B543">
-        <v>2012</v>
+        <v>2005</v>
       </c>
       <c r="C543">
-        <v>2488.848</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="544" spans="1:3">
       <c r="A544" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B544">
-        <v>2013</v>
+        <v>2006</v>
       </c>
       <c r="C544">
-        <v>2210.106</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="545" spans="1:3">
       <c r="A545" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B545">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="C545">
-        <v>1273.775</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="546" spans="1:3">
       <c r="A546" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B546">
-        <v>2015</v>
+        <v>2008</v>
       </c>
       <c r="C546">
-        <v>24.05</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="547" spans="1:3">
       <c r="A547" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B547">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="C547">
-        <v>186.57</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="548" spans="1:3">
       <c r="A548" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B548">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="C548">
-        <v>621.994</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="549" spans="1:3">
       <c r="A549" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B549">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="C549">
-        <v>2216.99</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="550" spans="1:3">
       <c r="A550" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B550">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C550">
-        <v>793.841</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="551" spans="1:3">
       <c r="A551" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B551">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C551">
-        <v>411.605</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="552" spans="1:3">
       <c r="A552" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B552">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C552">
-        <v>155.539</v>
+        <v>151</v>
       </c>
     </row>
     <row r="553" spans="1:3">
       <c r="A553" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B553">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C553">
-        <v>151.855</v>
+        <v>644</v>
       </c>
     </row>
     <row r="554" spans="1:3">
       <c r="A554" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B554">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C554">
-        <v>214.405</v>
+        <v>650</v>
       </c>
     </row>
     <row r="555" spans="1:3">
       <c r="A555" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B555">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="C555">
-        <v>286.399</v>
+        <v>657</v>
       </c>
     </row>
     <row r="556" spans="1:3">
       <c r="A556" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B556">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="C556">
-        <v>61.892</v>
+        <v>554.5</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -6543,10 +6543,10 @@
         <v>19</v>
       </c>
       <c r="B557">
-        <v>1989</v>
+        <v>2019</v>
       </c>
       <c r="C557">
-        <v>165.696</v>
+        <v>806</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -6554,10 +6554,10 @@
         <v>19</v>
       </c>
       <c r="B558">
-        <v>1990</v>
+        <v>2020</v>
       </c>
       <c r="C558">
-        <v>207.517</v>
+        <v>410</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -6565,10 +6565,10 @@
         <v>19</v>
       </c>
       <c r="B559">
-        <v>1991</v>
+        <v>2021</v>
       </c>
       <c r="C559">
-        <v>242.225</v>
+        <v>160</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -6576,10 +6576,10 @@
         <v>19</v>
       </c>
       <c r="B560">
-        <v>1992</v>
+        <v>2022</v>
       </c>
       <c r="C560">
-        <v>1116.246</v>
+        <v>176</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -6587,362 +6587,10 @@
         <v>19</v>
       </c>
       <c r="B561">
-        <v>1993</v>
+        <v>2023</v>
       </c>
       <c r="C561">
-        <v>148.56</v>
-      </c>
-    </row>
-    <row r="562" spans="1:3">
-      <c r="A562" t="s">
-        <v>19</v>
-      </c>
-      <c r="B562">
-        <v>1994</v>
-      </c>
-      <c r="C562">
-        <v>671.263</v>
-      </c>
-    </row>
-    <row r="563" spans="1:3">
-      <c r="A563" t="s">
-        <v>19</v>
-      </c>
-      <c r="B563">
-        <v>1995</v>
-      </c>
-      <c r="C563">
-        <v>868.654</v>
-      </c>
-    </row>
-    <row r="564" spans="1:3">
-      <c r="A564" t="s">
-        <v>19</v>
-      </c>
-      <c r="B564">
-        <v>1996</v>
-      </c>
-      <c r="C564">
-        <v>966.037</v>
-      </c>
-    </row>
-    <row r="565" spans="1:3">
-      <c r="A565" t="s">
-        <v>19</v>
-      </c>
-      <c r="B565">
-        <v>1997</v>
-      </c>
-      <c r="C565">
-        <v>2194.416</v>
-      </c>
-    </row>
-    <row r="566" spans="1:3">
-      <c r="A566" t="s">
-        <v>19</v>
-      </c>
-      <c r="B566">
-        <v>1998</v>
-      </c>
-      <c r="C566">
-        <v>1882.119</v>
-      </c>
-    </row>
-    <row r="567" spans="1:3">
-      <c r="A567" t="s">
-        <v>19</v>
-      </c>
-      <c r="B567">
-        <v>1999</v>
-      </c>
-      <c r="C567">
-        <v>1622.012</v>
-      </c>
-    </row>
-    <row r="568" spans="1:3">
-      <c r="A568" t="s">
-        <v>19</v>
-      </c>
-      <c r="B568">
-        <v>2000</v>
-      </c>
-      <c r="C568">
-        <v>1075.395</v>
-      </c>
-    </row>
-    <row r="569" spans="1:3">
-      <c r="A569" t="s">
-        <v>19</v>
-      </c>
-      <c r="B569">
-        <v>2001</v>
-      </c>
-      <c r="C569">
-        <v>847.7</v>
-      </c>
-    </row>
-    <row r="570" spans="1:3">
-      <c r="A570" t="s">
-        <v>19</v>
-      </c>
-      <c r="B570">
-        <v>2002</v>
-      </c>
-      <c r="C570">
-        <v>1751.447</v>
-      </c>
-    </row>
-    <row r="571" spans="1:3">
-      <c r="A571" t="s">
-        <v>19</v>
-      </c>
-      <c r="B571">
-        <v>2003</v>
-      </c>
-      <c r="C571">
-        <v>1398.02</v>
-      </c>
-    </row>
-    <row r="572" spans="1:3">
-      <c r="A572" t="s">
-        <v>19</v>
-      </c>
-      <c r="B572">
-        <v>2004</v>
-      </c>
-      <c r="C572">
-        <v>1085.991</v>
-      </c>
-    </row>
-    <row r="573" spans="1:3">
-      <c r="A573" t="s">
-        <v>19</v>
-      </c>
-      <c r="B573">
-        <v>2005</v>
-      </c>
-      <c r="C573">
-        <v>1460.566</v>
-      </c>
-    </row>
-    <row r="574" spans="1:3">
-      <c r="A574" t="s">
-        <v>19</v>
-      </c>
-      <c r="B574">
-        <v>2006</v>
-      </c>
-      <c r="C574">
-        <v>1937.453</v>
-      </c>
-    </row>
-    <row r="575" spans="1:3">
-      <c r="A575" t="s">
-        <v>19</v>
-      </c>
-      <c r="B575">
-        <v>2007</v>
-      </c>
-      <c r="C575">
-        <v>2292.716</v>
-      </c>
-    </row>
-    <row r="576" spans="1:3">
-      <c r="A576" t="s">
-        <v>19</v>
-      </c>
-      <c r="B576">
-        <v>2008</v>
-      </c>
-      <c r="C576">
-        <v>2033.549</v>
-      </c>
-    </row>
-    <row r="577" spans="1:3">
-      <c r="A577" t="s">
-        <v>19</v>
-      </c>
-      <c r="B577">
-        <v>2009</v>
-      </c>
-      <c r="C577">
-        <v>1373.338</v>
-      </c>
-    </row>
-    <row r="578" spans="1:3">
-      <c r="A578" t="s">
-        <v>19</v>
-      </c>
-      <c r="B578">
-        <v>2010</v>
-      </c>
-      <c r="C578">
-        <v>1442.3</v>
-      </c>
-    </row>
-    <row r="579" spans="1:3">
-      <c r="A579" t="s">
-        <v>19</v>
-      </c>
-      <c r="B579">
-        <v>2011</v>
-      </c>
-      <c r="C579">
-        <v>1911.578</v>
-      </c>
-    </row>
-    <row r="580" spans="1:3">
-      <c r="A580" t="s">
-        <v>19</v>
-      </c>
-      <c r="B580">
-        <v>2012</v>
-      </c>
-      <c r="C580">
-        <v>2488.848</v>
-      </c>
-    </row>
-    <row r="581" spans="1:3">
-      <c r="A581" t="s">
-        <v>19</v>
-      </c>
-      <c r="B581">
-        <v>2013</v>
-      </c>
-      <c r="C581">
-        <v>2210.106</v>
-      </c>
-    </row>
-    <row r="582" spans="1:3">
-      <c r="A582" t="s">
-        <v>19</v>
-      </c>
-      <c r="B582">
-        <v>2014</v>
-      </c>
-      <c r="C582">
-        <v>1273.775</v>
-      </c>
-    </row>
-    <row r="583" spans="1:3">
-      <c r="A583" t="s">
-        <v>19</v>
-      </c>
-      <c r="B583">
-        <v>2015</v>
-      </c>
-      <c r="C583">
-        <v>24.05</v>
-      </c>
-    </row>
-    <row r="584" spans="1:3">
-      <c r="A584" t="s">
-        <v>19</v>
-      </c>
-      <c r="B584">
-        <v>2016</v>
-      </c>
-      <c r="C584">
-        <v>186.57</v>
-      </c>
-    </row>
-    <row r="585" spans="1:3">
-      <c r="A585" t="s">
-        <v>19</v>
-      </c>
-      <c r="B585">
-        <v>2017</v>
-      </c>
-      <c r="C585">
-        <v>621.994</v>
-      </c>
-    </row>
-    <row r="586" spans="1:3">
-      <c r="A586" t="s">
-        <v>19</v>
-      </c>
-      <c r="B586">
-        <v>2018</v>
-      </c>
-      <c r="C586">
-        <v>2216.99</v>
-      </c>
-    </row>
-    <row r="587" spans="1:3">
-      <c r="A587" t="s">
-        <v>19</v>
-      </c>
-      <c r="B587">
-        <v>2019</v>
-      </c>
-      <c r="C587">
-        <v>793.841</v>
-      </c>
-    </row>
-    <row r="588" spans="1:3">
-      <c r="A588" t="s">
-        <v>19</v>
-      </c>
-      <c r="B588">
-        <v>2020</v>
-      </c>
-      <c r="C588">
-        <v>411.605</v>
-      </c>
-    </row>
-    <row r="589" spans="1:3">
-      <c r="A589" t="s">
-        <v>19</v>
-      </c>
-      <c r="B589">
-        <v>2021</v>
-      </c>
-      <c r="C589">
-        <v>155.539</v>
-      </c>
-    </row>
-    <row r="590" spans="1:3">
-      <c r="A590" t="s">
-        <v>19</v>
-      </c>
-      <c r="B590">
-        <v>2022</v>
-      </c>
-      <c r="C590">
-        <v>151.855</v>
-      </c>
-    </row>
-    <row r="591" spans="1:3">
-      <c r="A591" t="s">
-        <v>19</v>
-      </c>
-      <c r="B591">
-        <v>2023</v>
-      </c>
-      <c r="C591">
-        <v>214.405</v>
-      </c>
-    </row>
-    <row r="592" spans="1:3">
-      <c r="A592" t="s">
-        <v>19</v>
-      </c>
-      <c r="B592">
-        <v>2024</v>
-      </c>
-      <c r="C592">
-        <v>286.399</v>
-      </c>
-    </row>
-    <row r="593" spans="1:3">
-      <c r="A593" t="s">
-        <v>19</v>
-      </c>
-      <c r="B593">
-        <v>2025</v>
-      </c>
-      <c r="C593">
-        <v>61.892</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/cdat_macarellus_cmsy.xlsx
+++ b/Catch models/cdat_macarellus_cmsy.xlsx
@@ -716,7 +716,7 @@
         <v>2014</v>
       </c>
       <c r="C27">
-        <v>151</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1101,7 +1101,7 @@
         <v>2014</v>
       </c>
       <c r="C62">
-        <v>151</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1486,7 +1486,7 @@
         <v>2014</v>
       </c>
       <c r="C97">
-        <v>151</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1871,7 +1871,7 @@
         <v>2014</v>
       </c>
       <c r="C132">
-        <v>151</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2256,7 +2256,7 @@
         <v>2014</v>
       </c>
       <c r="C167">
-        <v>151</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -2641,7 +2641,7 @@
         <v>2014</v>
       </c>
       <c r="C202">
-        <v>151</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -3026,7 +3026,7 @@
         <v>2014</v>
       </c>
       <c r="C237">
-        <v>151</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -3411,7 +3411,7 @@
         <v>2014</v>
       </c>
       <c r="C272">
-        <v>151</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -3796,7 +3796,7 @@
         <v>2014</v>
       </c>
       <c r="C307">
-        <v>151</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -4181,7 +4181,7 @@
         <v>2014</v>
       </c>
       <c r="C342">
-        <v>151</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -4566,7 +4566,7 @@
         <v>2014</v>
       </c>
       <c r="C377">
-        <v>151</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -4951,7 +4951,7 @@
         <v>2014</v>
       </c>
       <c r="C412">
-        <v>151</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -5336,7 +5336,7 @@
         <v>2014</v>
       </c>
       <c r="C447">
-        <v>151</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -5721,7 +5721,7 @@
         <v>2014</v>
       </c>
       <c r="C482">
-        <v>151</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -6106,7 +6106,7 @@
         <v>2014</v>
       </c>
       <c r="C517">
-        <v>151</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="518" spans="1:3">
@@ -6491,7 +6491,7 @@
         <v>2014</v>
       </c>
       <c r="C552">
-        <v>151</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="553" spans="1:3">
